--- a/data/ams_weekly_data/Audio_Array/ads_report_week24.xlsx
+++ b/data/ams_weekly_data/Audio_Array/ads_report_week24.xlsx
@@ -731,7 +731,7 @@
         <v>5</v>
       </c>
       <c r="F11" t="n">
-        <v>1844</v>
+        <v>1843</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -1039,7 +1039,7 @@
         <v>7</v>
       </c>
       <c r="F22" t="n">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1123,7 +1123,7 @@
         <v>52</v>
       </c>
       <c r="F25" t="n">
-        <v>5297</v>
+        <v>5288</v>
       </c>
       <c r="G25" t="n">
         <v>5464.41</v>
@@ -1179,7 +1179,7 @@
         <v>10</v>
       </c>
       <c r="F27" t="n">
-        <v>2256</v>
+        <v>2255</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1291,7 +1291,7 @@
         <v>13</v>
       </c>
       <c r="F31" t="n">
-        <v>1679</v>
+        <v>1674</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1347,7 +1347,7 @@
         <v>45</v>
       </c>
       <c r="F33" t="n">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="G33" t="n">
         <v>2880.51</v>
@@ -1375,7 +1375,7 @@
         <v>16</v>
       </c>
       <c r="F34" t="n">
-        <v>2735</v>
+        <v>2734</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>4</v>
       </c>
       <c r="F35" t="n">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1431,7 +1431,7 @@
         <v>4</v>
       </c>
       <c r="F36" t="n">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1543,7 +1543,7 @@
         <v>5</v>
       </c>
       <c r="F40" t="n">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="G40" t="n">
         <v>422.88</v>
@@ -1938,10 +1938,10 @@
         <v>12393</v>
       </c>
       <c r="G54" t="n">
-        <v>12200.85</v>
+        <v>16267.8</v>
       </c>
       <c r="H54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
@@ -1991,7 +1991,7 @@
         <v>1</v>
       </c>
       <c r="F56" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -2131,7 +2131,7 @@
         <v>12</v>
       </c>
       <c r="F61" t="n">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2803,7 +2803,7 @@
         <v>3</v>
       </c>
       <c r="F85" t="n">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -3447,7 +3447,7 @@
         <v>33</v>
       </c>
       <c r="F108" t="n">
-        <v>5040</v>
+        <v>5033</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -7199,7 +7199,7 @@
         <v>10</v>
       </c>
       <c r="F242" t="n">
-        <v>1537</v>
+        <v>1533</v>
       </c>
       <c r="G242" t="n">
         <v>1100.85</v>
@@ -7227,7 +7227,7 @@
         <v>0</v>
       </c>
       <c r="F243" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -7255,7 +7255,7 @@
         <v>1</v>
       </c>
       <c r="F244" t="n">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
         <v>13</v>
       </c>
       <c r="F251" t="n">
-        <v>3418</v>
+        <v>3407</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -7479,7 +7479,7 @@
         <v>15</v>
       </c>
       <c r="F252" t="n">
-        <v>5018</v>
+        <v>5002</v>
       </c>
       <c r="G252" t="n">
         <v>4066.95</v>
@@ -7507,7 +7507,7 @@
         <v>3</v>
       </c>
       <c r="F253" t="n">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G253" t="n">
         <v>0</v>
@@ -7787,7 +7787,7 @@
         <v>22</v>
       </c>
       <c r="F263" t="n">
-        <v>3256</v>
+        <v>3238</v>
       </c>
       <c r="G263" t="n">
         <v>2880.51</v>
@@ -11119,7 +11119,7 @@
         <v>20</v>
       </c>
       <c r="F382" t="n">
-        <v>3738</v>
+        <v>3736</v>
       </c>
       <c r="G382" t="n">
         <v>550</v>

--- a/data/ams_weekly_data/Audio_Array/ads_report_week24.xlsx
+++ b/data/ams_weekly_data/Audio_Array/ads_report_week24.xlsx
@@ -2439,7 +2439,7 @@
         <v>10</v>
       </c>
       <c r="F72" t="n">
-        <v>2229</v>
+        <v>2230</v>
       </c>
       <c r="G72" t="n">
         <v>1007.63</v>
@@ -2946,10 +2946,10 @@
         <v>20212</v>
       </c>
       <c r="G90" t="n">
-        <v>29656.8</v>
+        <v>23725.44</v>
       </c>
       <c r="H90" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91">
@@ -9274,10 +9274,10 @@
         <v>3270</v>
       </c>
       <c r="G316" t="n">
-        <v>507.63</v>
+        <v>0</v>
       </c>
       <c r="H316" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="317">
@@ -10114,10 +10114,10 @@
         <v>3607</v>
       </c>
       <c r="G346" t="n">
-        <v>28173.74</v>
+        <v>18089.84</v>
       </c>
       <c r="H346" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="347">
@@ -12575,7 +12575,7 @@
         <v>381</v>
       </c>
       <c r="F27" t="n">
-        <v>102268</v>
+        <v>102244</v>
       </c>
       <c r="G27" t="n">
         <v>5931.36</v>
@@ -12911,7 +12911,7 @@
         <v>674</v>
       </c>
       <c r="F39" t="n">
-        <v>177895</v>
+        <v>177893</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>

--- a/data/ams_weekly_data/Audio_Array/ads_report_week24.xlsx
+++ b/data/ams_weekly_data/Audio_Array/ads_report_week24.xlsx
@@ -14135,7 +14135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14198,19 +14198,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>27384</v>
+        <v>11163</v>
       </c>
       <c r="E2" t="n">
-        <v>153</v>
+        <v>62</v>
       </c>
       <c r="F2" t="n">
-        <v>2561.09</v>
+        <v>1044.066071787869</v>
       </c>
       <c r="G2" t="n">
-        <v>5506.780000000001</v>
+        <v>2244.92</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -14222,28 +14222,28 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Audio Array-B0BLJVJ2GN-AA 05 Suspension-SB-PT</t>
+          <t>Audio Array-B0B4DPX2J2-Condenser AM C1-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B0B4G8PH2P</t>
+          <t>B0CF5R3V95</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18658</v>
+        <v>16221</v>
       </c>
       <c r="E3" t="n">
-        <v>206</v>
+        <v>91</v>
       </c>
       <c r="F3" t="n">
-        <v>2778.746666666666</v>
+        <v>1517.023928212131</v>
       </c>
       <c r="G3" t="n">
-        <v>9951.690000000001</v>
+        <v>3261.86</v>
       </c>
       <c r="H3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -14260,23 +14260,23 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B0BLJVJ2GN</t>
+          <t>B0B4G8PH2P</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18658</v>
+        <v>14078</v>
       </c>
       <c r="E4" t="n">
-        <v>206</v>
+        <v>156</v>
       </c>
       <c r="F4" t="n">
-        <v>2778.746666666666</v>
+        <v>2096.581405689265</v>
       </c>
       <c r="G4" t="n">
-        <v>9951.690000000001</v>
+        <v>7508.611151736442</v>
       </c>
       <c r="H4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -14293,23 +14293,23 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B0CF5R3V95</t>
+          <t>B0BLJVJ2GN</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18658</v>
+        <v>14172</v>
       </c>
       <c r="E5" t="n">
-        <v>206</v>
+        <v>157</v>
       </c>
       <c r="F5" t="n">
-        <v>2778.746666666666</v>
+        <v>2110.564857215983</v>
       </c>
       <c r="G5" t="n">
-        <v>9951.690000000001</v>
+        <v>7558.690914815696</v>
       </c>
       <c r="H5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -14321,28 +14321,28 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Audio Array-B0BPLZ5CGV-AI 04 Audio Interface-SBV -PT</t>
+          <t>Audio Array-B0BLJVJ2GN-AA 05 Suspension-SB-PT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0CF5R3V95</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>82240</v>
+        <v>16810</v>
       </c>
       <c r="E6" t="n">
-        <v>621</v>
+        <v>186</v>
       </c>
       <c r="F6" t="n">
-        <v>5743.17</v>
+        <v>2503.406212784919</v>
       </c>
       <c r="G6" t="n">
-        <v>36602.54</v>
+        <v>8965.596926327536</v>
       </c>
       <c r="H6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -14354,25 +14354,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Audio Array-B0CKHVHVQ1-AM W45 Wireless-SBV-KT-Phrase</t>
+          <t>Audio Array-B0BLJVJ2GN-AA 05 Suspension-SB-PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0CKHVHVQ1</t>
+          <t>B0D3M86SH1</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>19575</v>
+        <v>10916</v>
       </c>
       <c r="E7" t="n">
-        <v>85</v>
+        <v>121</v>
       </c>
       <c r="F7" t="n">
-        <v>1245.08</v>
+        <v>1625.687524309833</v>
       </c>
       <c r="G7" t="n">
-        <v>17623.72</v>
+        <v>5822.171007120328</v>
       </c>
       <c r="H7" t="n">
         <v>4</v>
@@ -14387,28 +14387,28 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Audio Array-B0CKHVHVQ1-AM W45 Wireless-SBV-KT-Phrase (2)</t>
+          <t>Audio Array-B0BPLZ5CGV-AI 04 Audio Interface-SBV -PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0CKHVHVQ1</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>24091</v>
+        <v>82240</v>
       </c>
       <c r="E8" t="n">
-        <v>146</v>
+        <v>621</v>
       </c>
       <c r="F8" t="n">
-        <v>1053.12</v>
+        <v>5743.17</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>36602.54</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -14420,7 +14420,7 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Audio Array-B0CKHVHVQ1-AM W45 Wireless-SBV-PT</t>
+          <t>Audio Array-B0CKHVHVQ1-AM W45 Wireless-SBV-KT-Phrase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -14429,19 +14429,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>60085</v>
+        <v>19575</v>
       </c>
       <c r="E9" t="n">
-        <v>465</v>
+        <v>85</v>
       </c>
       <c r="F9" t="n">
-        <v>2410.22</v>
+        <v>1245.08</v>
       </c>
       <c r="G9" t="n">
-        <v>4405.93</v>
+        <v>17623.72</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -14453,22 +14453,22 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Audio Array-B0DXFPM4N2-Studio Monitor- SBV-CT</t>
+          <t>Audio Array-B0CKHVHVQ1-AM W45 Wireless-SBV-KT-Phrase (2)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B0DXFPM4N2</t>
+          <t>B0CKHVHVQ1</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>19117</v>
+        <v>24091</v>
       </c>
       <c r="E10" t="n">
-        <v>249</v>
+        <v>146</v>
       </c>
       <c r="F10" t="n">
-        <v>2475.71</v>
+        <v>1053.12</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -14486,28 +14486,28 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Audio Array-Catch All-Condenser -SB-PT</t>
+          <t>Audio Array-B0CKHVHVQ1-AM W45 Wireless-SBV-PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B0B4DPX2J2</t>
+          <t>B0CKHVHVQ1</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13680</v>
+        <v>60085</v>
       </c>
       <c r="E11" t="n">
-        <v>143</v>
+        <v>465</v>
       </c>
       <c r="F11" t="n">
-        <v>2123.736666666667</v>
+        <v>2410.22</v>
       </c>
       <c r="G11" t="n">
-        <v>5718.37</v>
+        <v>4405.93</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -14519,28 +14519,28 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Audio Array-Catch All-Condenser -SB-PT</t>
+          <t>Audio Array-B0DXFPM4N2-Studio Monitor- SBV-CT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B0D3M1B4Z8</t>
+          <t>B0DXFPM4N2</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13680</v>
+        <v>19117</v>
       </c>
       <c r="E12" t="n">
-        <v>143</v>
+        <v>249</v>
       </c>
       <c r="F12" t="n">
-        <v>2123.736666666667</v>
+        <v>2475.71</v>
       </c>
       <c r="G12" t="n">
-        <v>5718.37</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -14557,23 +14557,23 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B0FF9R3GKK</t>
+          <t>B0B4DPX2J2</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13680</v>
+        <v>21483</v>
       </c>
       <c r="E13" t="n">
-        <v>143</v>
+        <v>224</v>
       </c>
       <c r="F13" t="n">
-        <v>2123.736666666667</v>
+        <v>3334.949587195885</v>
       </c>
       <c r="G13" t="n">
-        <v>5718.37</v>
+        <v>8979.68</v>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -14585,28 +14585,28 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+          <t>Audio Array-Catch All-Condenser -SB-PT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0B4DPX2J2</t>
+          <t>B0D3M1B4Z8</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>7115</v>
+        <v>13782</v>
       </c>
       <c r="E14" t="n">
-        <v>43</v>
+        <v>144</v>
       </c>
       <c r="F14" t="n">
-        <v>510.1089655172414</v>
+        <v>2139.576384773983</v>
       </c>
       <c r="G14" t="n">
-        <v>2633.401724137931</v>
+        <v>5761.02</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -14618,25 +14618,25 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+          <t>Audio Array-Catch All-Condenser -SB-PT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0B4DS678Q</t>
+          <t>B0FF9R3GKK</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>7115</v>
+        <v>5776</v>
       </c>
       <c r="E15" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="F15" t="n">
-        <v>510.1089655172414</v>
+        <v>896.684028030132</v>
       </c>
       <c r="G15" t="n">
-        <v>2633.401724137931</v>
+        <v>2414.41</v>
       </c>
       <c r="H15" t="n">
         <v>1</v>
@@ -14656,23 +14656,23 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0B4G19R58</t>
+          <t>B0B4DPX2J2</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>7115</v>
+        <v>26126</v>
       </c>
       <c r="E16" t="n">
-        <v>43</v>
+        <v>136</v>
       </c>
       <c r="F16" t="n">
-        <v>510.1089655172414</v>
+        <v>2020.133718092619</v>
       </c>
       <c r="G16" t="n">
-        <v>2633.401724137931</v>
+        <v>6734.760000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -14689,23 +14689,23 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0B4G1PXWV</t>
+          <t>B0B4K87PR4</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>7115</v>
+        <v>28565</v>
       </c>
       <c r="E17" t="n">
-        <v>43</v>
+        <v>144</v>
       </c>
       <c r="F17" t="n">
-        <v>510.1089655172414</v>
+        <v>1227.582149132192</v>
       </c>
       <c r="G17" t="n">
-        <v>2633.401724137931</v>
+        <v>6777.959999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -14722,23 +14722,23 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0B4G89VQJ</t>
+          <t>B0BLJVJ2GN</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>7115</v>
+        <v>1153</v>
       </c>
       <c r="E18" t="n">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="F18" t="n">
-        <v>510.1089655172414</v>
+        <v>242.4426520898196</v>
       </c>
       <c r="G18" t="n">
-        <v>2633.401724137931</v>
+        <v>550</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -14755,23 +14755,23 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0B4JRQP22</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>7115</v>
+        <v>49181</v>
       </c>
       <c r="E19" t="n">
-        <v>43</v>
+        <v>372</v>
       </c>
       <c r="F19" t="n">
-        <v>510.1089655172414</v>
+        <v>4289.9</v>
       </c>
       <c r="G19" t="n">
-        <v>2633.401724137931</v>
+        <v>34780.52</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -14788,23 +14788,23 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0B4K87PR4</t>
+          <t>B0CF5TCQKL</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>7115</v>
+        <v>13566</v>
       </c>
       <c r="E20" t="n">
-        <v>43</v>
+        <v>149</v>
       </c>
       <c r="F20" t="n">
-        <v>510.1089655172414</v>
+        <v>2852.52734791018</v>
       </c>
       <c r="G20" t="n">
-        <v>2633.401724137931</v>
+        <v>6471.18</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -14821,23 +14821,23 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0B4KC7VBM</t>
+          <t>B0CKHVHVQ1</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>7115</v>
+        <v>74274</v>
       </c>
       <c r="E21" t="n">
-        <v>43</v>
+        <v>376</v>
       </c>
       <c r="F21" t="n">
-        <v>510.1089655172414</v>
+        <v>3191.899048283553</v>
       </c>
       <c r="G21" t="n">
-        <v>2633.401724137931</v>
+        <v>17623.72</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -14854,20 +14854,20 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0BLJVJ2GN</t>
+          <t>B0D3LZWTHV</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>7115</v>
+        <v>11339</v>
       </c>
       <c r="E22" t="n">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="F22" t="n">
-        <v>510.1089655172414</v>
+        <v>876.7362819073812</v>
       </c>
       <c r="G22" t="n">
-        <v>2633.401724137931</v>
+        <v>2922.88</v>
       </c>
       <c r="H22" t="n">
         <v>1</v>
@@ -14887,652 +14887,25 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0BLK8DNPD</t>
+          <t>B0DT6T6N6B</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>7115</v>
+        <v>2139</v>
       </c>
       <c r="E23" t="n">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="F23" t="n">
-        <v>510.1089655172414</v>
+        <v>91.93880258425463</v>
       </c>
       <c r="G23" t="n">
-        <v>2633.401724137931</v>
+        <v>507.63</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>B0BPLZ5CGV</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>7115</v>
-      </c>
-      <c r="E24" t="n">
-        <v>43</v>
-      </c>
-      <c r="F24" t="n">
-        <v>510.1089655172414</v>
-      </c>
-      <c r="G24" t="n">
-        <v>2633.401724137931</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>B0C4YTNJG7</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>7115</v>
-      </c>
-      <c r="E25" t="n">
-        <v>43</v>
-      </c>
-      <c r="F25" t="n">
-        <v>510.1089655172414</v>
-      </c>
-      <c r="G25" t="n">
-        <v>2633.401724137931</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>B0C539RBGL</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>7115</v>
-      </c>
-      <c r="E26" t="n">
-        <v>43</v>
-      </c>
-      <c r="F26" t="n">
-        <v>510.1089655172414</v>
-      </c>
-      <c r="G26" t="n">
-        <v>2633.401724137931</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>B0CF5R3V95</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>7115</v>
-      </c>
-      <c r="E27" t="n">
-        <v>43</v>
-      </c>
-      <c r="F27" t="n">
-        <v>510.1089655172414</v>
-      </c>
-      <c r="G27" t="n">
-        <v>2633.401724137931</v>
-      </c>
-      <c r="H27" t="n">
-        <v>1</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>B0CF5RRTDJ</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>7115</v>
-      </c>
-      <c r="E28" t="n">
-        <v>43</v>
-      </c>
-      <c r="F28" t="n">
-        <v>510.1089655172414</v>
-      </c>
-      <c r="G28" t="n">
-        <v>2633.401724137931</v>
-      </c>
-      <c r="H28" t="n">
-        <v>1</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>B0CF5TCQKL</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>7115</v>
-      </c>
-      <c r="E29" t="n">
-        <v>43</v>
-      </c>
-      <c r="F29" t="n">
-        <v>510.1089655172414</v>
-      </c>
-      <c r="G29" t="n">
-        <v>2633.401724137931</v>
-      </c>
-      <c r="H29" t="n">
-        <v>1</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>B0CH4RT4P8</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>7115</v>
-      </c>
-      <c r="E30" t="n">
-        <v>43</v>
-      </c>
-      <c r="F30" t="n">
-        <v>510.1089655172414</v>
-      </c>
-      <c r="G30" t="n">
-        <v>2633.401724137931</v>
-      </c>
-      <c r="H30" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>B0CKHVHVQ1</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>7115</v>
-      </c>
-      <c r="E31" t="n">
-        <v>43</v>
-      </c>
-      <c r="F31" t="n">
-        <v>510.1089655172414</v>
-      </c>
-      <c r="G31" t="n">
-        <v>2633.401724137931</v>
-      </c>
-      <c r="H31" t="n">
-        <v>1</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>B0CM6NTWBP</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>7115</v>
-      </c>
-      <c r="E32" t="n">
-        <v>43</v>
-      </c>
-      <c r="F32" t="n">
-        <v>510.1089655172414</v>
-      </c>
-      <c r="G32" t="n">
-        <v>2633.401724137931</v>
-      </c>
-      <c r="H32" t="n">
-        <v>1</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>B0D3M1B4Z8</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>7115</v>
-      </c>
-      <c r="E33" t="n">
-        <v>43</v>
-      </c>
-      <c r="F33" t="n">
-        <v>510.1089655172414</v>
-      </c>
-      <c r="G33" t="n">
-        <v>2633.401724137931</v>
-      </c>
-      <c r="H33" t="n">
-        <v>1</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>B0DFMLS8JG</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>7115</v>
-      </c>
-      <c r="E34" t="n">
-        <v>43</v>
-      </c>
-      <c r="F34" t="n">
-        <v>510.1089655172414</v>
-      </c>
-      <c r="G34" t="n">
-        <v>2633.401724137931</v>
-      </c>
-      <c r="H34" t="n">
-        <v>1</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>B0DFMMTWLY</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>7115</v>
-      </c>
-      <c r="E35" t="n">
-        <v>43</v>
-      </c>
-      <c r="F35" t="n">
-        <v>510.1089655172414</v>
-      </c>
-      <c r="G35" t="n">
-        <v>2633.401724137931</v>
-      </c>
-      <c r="H35" t="n">
-        <v>1</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>B0DFMNGFTD</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>7115</v>
-      </c>
-      <c r="E36" t="n">
-        <v>43</v>
-      </c>
-      <c r="F36" t="n">
-        <v>510.1089655172414</v>
-      </c>
-      <c r="G36" t="n">
-        <v>2633.401724137931</v>
-      </c>
-      <c r="H36" t="n">
-        <v>1</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>B0DT6T6N6B</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>7115</v>
-      </c>
-      <c r="E37" t="n">
-        <v>43</v>
-      </c>
-      <c r="F37" t="n">
-        <v>510.1089655172414</v>
-      </c>
-      <c r="G37" t="n">
-        <v>2633.401724137931</v>
-      </c>
-      <c r="H37" t="n">
-        <v>1</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>B0FF9R3GKK</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>7115</v>
-      </c>
-      <c r="E38" t="n">
-        <v>43</v>
-      </c>
-      <c r="F38" t="n">
-        <v>510.1089655172414</v>
-      </c>
-      <c r="G38" t="n">
-        <v>2633.401724137931</v>
-      </c>
-      <c r="H38" t="n">
-        <v>1</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>B0G2C2RCXN</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>7115</v>
-      </c>
-      <c r="E39" t="n">
-        <v>43</v>
-      </c>
-      <c r="F39" t="n">
-        <v>510.1089655172414</v>
-      </c>
-      <c r="G39" t="n">
-        <v>2633.401724137931</v>
-      </c>
-      <c r="H39" t="n">
-        <v>1</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>B0G3Q517Y2</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>7115</v>
-      </c>
-      <c r="E40" t="n">
-        <v>43</v>
-      </c>
-      <c r="F40" t="n">
-        <v>510.1089655172414</v>
-      </c>
-      <c r="G40" t="n">
-        <v>2633.401724137931</v>
-      </c>
-      <c r="H40" t="n">
-        <v>1</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>B0G3Q59X8C</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>7115</v>
-      </c>
-      <c r="E41" t="n">
-        <v>43</v>
-      </c>
-      <c r="F41" t="n">
-        <v>510.1089655172414</v>
-      </c>
-      <c r="G41" t="n">
-        <v>2633.401724137931</v>
-      </c>
-      <c r="H41" t="n">
-        <v>1</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>B0G4DNF8RZ</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>7115</v>
-      </c>
-      <c r="E42" t="n">
-        <v>43</v>
-      </c>
-      <c r="F42" t="n">
-        <v>510.1089655172414</v>
-      </c>
-      <c r="G42" t="n">
-        <v>2633.401724137931</v>
-      </c>
-      <c r="H42" t="n">
-        <v>1</v>
-      </c>
-      <c r="I42" t="inlineStr">
         <is>
           <t>Audio Array</t>
         </is>

--- a/data/ams_weekly_data/Audio_Array/ads_report_week24.xlsx
+++ b/data/ams_weekly_data/Audio_Array/ads_report_week24.xlsx
@@ -3170,10 +3170,10 @@
         <v>33375</v>
       </c>
       <c r="G98" t="n">
-        <v>4236.44</v>
+        <v>5930.509999999999</v>
       </c>
       <c r="H98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99">

--- a/data/ams_weekly_data/Audio_Array/ads_report_week24.xlsx
+++ b/data/ams_weekly_data/Audio_Array/ads_report_week24.xlsx
@@ -1042,10 +1042,10 @@
         <v>7228</v>
       </c>
       <c r="G22" t="n">
-        <v>2541.53</v>
+        <v>4828.82</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -3114,10 +3114,10 @@
         <v>30950</v>
       </c>
       <c r="G96" t="n">
-        <v>74142.36</v>
+        <v>67787.28</v>
       </c>
       <c r="H96" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="97">
@@ -14135,7 +14135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14198,19 +14198,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11163</v>
+        <v>27384</v>
       </c>
       <c r="E2" t="n">
-        <v>62</v>
+        <v>153</v>
       </c>
       <c r="F2" t="n">
-        <v>1044.066071787869</v>
+        <v>2561.09</v>
       </c>
       <c r="G2" t="n">
-        <v>2244.92</v>
+        <v>5506.780000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -14222,28 +14222,28 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Audio Array-B0B4DPX2J2-Condenser AM C1-SBV-KT-Exact/Phrase</t>
+          <t>Audio Array-B0BLJVJ2GN-AA 05 Suspension-SB-PT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B0CF5R3V95</t>
+          <t>B0B4G8PH2P</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16221</v>
+        <v>18658</v>
       </c>
       <c r="E3" t="n">
-        <v>91</v>
+        <v>206</v>
       </c>
       <c r="F3" t="n">
-        <v>1517.023928212131</v>
+        <v>2778.746666666666</v>
       </c>
       <c r="G3" t="n">
-        <v>3261.86</v>
+        <v>9951.690000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -14260,23 +14260,23 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B0B4G8PH2P</t>
+          <t>B0BLJVJ2GN</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14078</v>
+        <v>18658</v>
       </c>
       <c r="E4" t="n">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="F4" t="n">
-        <v>2096.581405689265</v>
+        <v>2778.746666666666</v>
       </c>
       <c r="G4" t="n">
-        <v>7508.611151736442</v>
+        <v>9951.690000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -14293,23 +14293,23 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B0BLJVJ2GN</t>
+          <t>B0CF5R3V95</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14172</v>
+        <v>18658</v>
       </c>
       <c r="E5" t="n">
-        <v>157</v>
+        <v>206</v>
       </c>
       <c r="F5" t="n">
-        <v>2110.564857215983</v>
+        <v>2778.746666666666</v>
       </c>
       <c r="G5" t="n">
-        <v>7558.690914815696</v>
+        <v>9951.690000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -14321,28 +14321,28 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Audio Array-B0BLJVJ2GN-AA 05 Suspension-SB-PT</t>
+          <t>Audio Array-B0BPLZ5CGV-AI 04 Audio Interface-SBV -PT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B0CF5R3V95</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16810</v>
+        <v>82240</v>
       </c>
       <c r="E6" t="n">
-        <v>186</v>
+        <v>621</v>
       </c>
       <c r="F6" t="n">
-        <v>2503.406212784919</v>
+        <v>5743.17</v>
       </c>
       <c r="G6" t="n">
-        <v>8965.596926327536</v>
+        <v>36602.54</v>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -14354,25 +14354,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Audio Array-B0BLJVJ2GN-AA 05 Suspension-SB-PT</t>
+          <t>Audio Array-B0CKHVHVQ1-AM W45 Wireless-SBV-KT-Phrase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0D3M86SH1</t>
+          <t>B0CKHVHVQ1</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10916</v>
+        <v>19575</v>
       </c>
       <c r="E7" t="n">
-        <v>121</v>
+        <v>85</v>
       </c>
       <c r="F7" t="n">
-        <v>1625.687524309833</v>
+        <v>1245.08</v>
       </c>
       <c r="G7" t="n">
-        <v>5822.171007120328</v>
+        <v>17623.72</v>
       </c>
       <c r="H7" t="n">
         <v>4</v>
@@ -14387,28 +14387,28 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Audio Array-B0BPLZ5CGV-AI 04 Audio Interface-SBV -PT</t>
+          <t>Audio Array-B0CKHVHVQ1-AM W45 Wireless-SBV-KT-Phrase (2)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0CKHVHVQ1</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>82240</v>
+        <v>24091</v>
       </c>
       <c r="E8" t="n">
-        <v>621</v>
+        <v>146</v>
       </c>
       <c r="F8" t="n">
-        <v>5743.17</v>
+        <v>1053.12</v>
       </c>
       <c r="G8" t="n">
-        <v>36602.54</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -14420,7 +14420,7 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Audio Array-B0CKHVHVQ1-AM W45 Wireless-SBV-KT-Phrase</t>
+          <t>Audio Array-B0CKHVHVQ1-AM W45 Wireless-SBV-PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -14429,19 +14429,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>19575</v>
+        <v>60085</v>
       </c>
       <c r="E9" t="n">
-        <v>85</v>
+        <v>465</v>
       </c>
       <c r="F9" t="n">
-        <v>1245.08</v>
+        <v>2410.22</v>
       </c>
       <c r="G9" t="n">
-        <v>17623.72</v>
+        <v>4405.93</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -14453,22 +14453,22 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Audio Array-B0CKHVHVQ1-AM W45 Wireless-SBV-KT-Phrase (2)</t>
+          <t>Audio Array-B0DXFPM4N2-Studio Monitor- SBV-CT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B0CKHVHVQ1</t>
+          <t>B0DXFPM4N2</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>24091</v>
+        <v>19117</v>
       </c>
       <c r="E10" t="n">
-        <v>146</v>
+        <v>249</v>
       </c>
       <c r="F10" t="n">
-        <v>1053.12</v>
+        <v>2475.71</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -14486,28 +14486,28 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Audio Array-B0CKHVHVQ1-AM W45 Wireless-SBV-PT</t>
+          <t>Audio Array-Catch All-Condenser -SB-PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B0CKHVHVQ1</t>
+          <t>B0B4DPX2J2</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>60085</v>
+        <v>13680</v>
       </c>
       <c r="E11" t="n">
-        <v>465</v>
+        <v>143</v>
       </c>
       <c r="F11" t="n">
-        <v>2410.22</v>
+        <v>2123.736666666667</v>
       </c>
       <c r="G11" t="n">
-        <v>4405.93</v>
+        <v>5718.37</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -14519,28 +14519,28 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Audio Array-B0DXFPM4N2-Studio Monitor- SBV-CT</t>
+          <t>Audio Array-Catch All-Condenser -SB-PT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B0DXFPM4N2</t>
+          <t>B0D3M1B4Z8</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>19117</v>
+        <v>13680</v>
       </c>
       <c r="E12" t="n">
-        <v>249</v>
+        <v>143</v>
       </c>
       <c r="F12" t="n">
-        <v>2475.71</v>
+        <v>2123.736666666667</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>5718.37</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -14557,23 +14557,23 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B0B4DPX2J2</t>
+          <t>B0FF9R3GKK</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>21483</v>
+        <v>13680</v>
       </c>
       <c r="E13" t="n">
-        <v>224</v>
+        <v>143</v>
       </c>
       <c r="F13" t="n">
-        <v>3334.949587195885</v>
+        <v>2123.736666666667</v>
       </c>
       <c r="G13" t="n">
-        <v>8979.68</v>
+        <v>5718.37</v>
       </c>
       <c r="H13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -14585,28 +14585,28 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Audio Array-Catch All-Condenser -SB-PT</t>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0D3M1B4Z8</t>
+          <t>B0B4DPX2J2</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13782</v>
+        <v>7115</v>
       </c>
       <c r="E14" t="n">
-        <v>144</v>
+        <v>43</v>
       </c>
       <c r="F14" t="n">
-        <v>2139.576384773983</v>
+        <v>510.1089655172414</v>
       </c>
       <c r="G14" t="n">
-        <v>5761.02</v>
+        <v>2633.401724137931</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -14618,25 +14618,25 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Audio Array-Catch All-Condenser -SB-PT</t>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0FF9R3GKK</t>
+          <t>B0B4DS678Q</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5776</v>
+        <v>7115</v>
       </c>
       <c r="E15" t="n">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="F15" t="n">
-        <v>896.684028030132</v>
+        <v>510.1089655172414</v>
       </c>
       <c r="G15" t="n">
-        <v>2414.41</v>
+        <v>2633.401724137931</v>
       </c>
       <c r="H15" t="n">
         <v>1</v>
@@ -14656,23 +14656,23 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0B4DPX2J2</t>
+          <t>B0B4G19R58</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>26126</v>
+        <v>7115</v>
       </c>
       <c r="E16" t="n">
-        <v>136</v>
+        <v>43</v>
       </c>
       <c r="F16" t="n">
-        <v>2020.133718092619</v>
+        <v>510.1089655172414</v>
       </c>
       <c r="G16" t="n">
-        <v>6734.760000000001</v>
+        <v>2633.401724137931</v>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -14689,23 +14689,23 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0B4K87PR4</t>
+          <t>B0B4G1PXWV</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>28565</v>
+        <v>7115</v>
       </c>
       <c r="E17" t="n">
-        <v>144</v>
+        <v>43</v>
       </c>
       <c r="F17" t="n">
-        <v>1227.582149132192</v>
+        <v>510.1089655172414</v>
       </c>
       <c r="G17" t="n">
-        <v>6777.959999999999</v>
+        <v>2633.401724137931</v>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -14722,23 +14722,23 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0BLJVJ2GN</t>
+          <t>B0B4G89VQJ</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1153</v>
+        <v>7115</v>
       </c>
       <c r="E18" t="n">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="F18" t="n">
-        <v>242.4426520898196</v>
+        <v>510.1089655172414</v>
       </c>
       <c r="G18" t="n">
-        <v>550</v>
+        <v>2633.401724137931</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -14755,23 +14755,23 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0B4JRQP22</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>49181</v>
+        <v>7115</v>
       </c>
       <c r="E19" t="n">
-        <v>372</v>
+        <v>43</v>
       </c>
       <c r="F19" t="n">
-        <v>4289.9</v>
+        <v>510.1089655172414</v>
       </c>
       <c r="G19" t="n">
-        <v>34780.52</v>
+        <v>2633.401724137931</v>
       </c>
       <c r="H19" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -14788,23 +14788,23 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0CF5TCQKL</t>
+          <t>B0B4K87PR4</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13566</v>
+        <v>7115</v>
       </c>
       <c r="E20" t="n">
-        <v>149</v>
+        <v>43</v>
       </c>
       <c r="F20" t="n">
-        <v>2852.52734791018</v>
+        <v>510.1089655172414</v>
       </c>
       <c r="G20" t="n">
-        <v>6471.18</v>
+        <v>2633.401724137931</v>
       </c>
       <c r="H20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -14821,23 +14821,23 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0CKHVHVQ1</t>
+          <t>B0B4KC7VBM</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>74274</v>
+        <v>7115</v>
       </c>
       <c r="E21" t="n">
-        <v>376</v>
+        <v>43</v>
       </c>
       <c r="F21" t="n">
-        <v>3191.899048283553</v>
+        <v>510.1089655172414</v>
       </c>
       <c r="G21" t="n">
-        <v>17623.72</v>
+        <v>2633.401724137931</v>
       </c>
       <c r="H21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -14854,20 +14854,20 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0D3LZWTHV</t>
+          <t>B0BLJVJ2GN</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11339</v>
+        <v>7115</v>
       </c>
       <c r="E22" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="F22" t="n">
-        <v>876.7362819073812</v>
+        <v>510.1089655172414</v>
       </c>
       <c r="G22" t="n">
-        <v>2922.88</v>
+        <v>2633.401724137931</v>
       </c>
       <c r="H22" t="n">
         <v>1</v>
@@ -14887,25 +14887,652 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>B0BLK8DNPD</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>7115</v>
+      </c>
+      <c r="E23" t="n">
+        <v>43</v>
+      </c>
+      <c r="F23" t="n">
+        <v>510.1089655172414</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2633.401724137931</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>B0BPLZ5CGV</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>7115</v>
+      </c>
+      <c r="E24" t="n">
+        <v>43</v>
+      </c>
+      <c r="F24" t="n">
+        <v>510.1089655172414</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2633.401724137931</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>B0C4YTNJG7</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>7115</v>
+      </c>
+      <c r="E25" t="n">
+        <v>43</v>
+      </c>
+      <c r="F25" t="n">
+        <v>510.1089655172414</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2633.401724137931</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>B0C539RBGL</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>7115</v>
+      </c>
+      <c r="E26" t="n">
+        <v>43</v>
+      </c>
+      <c r="F26" t="n">
+        <v>510.1089655172414</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2633.401724137931</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>B0CF5R3V95</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>7115</v>
+      </c>
+      <c r="E27" t="n">
+        <v>43</v>
+      </c>
+      <c r="F27" t="n">
+        <v>510.1089655172414</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2633.401724137931</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>B0CF5RRTDJ</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>7115</v>
+      </c>
+      <c r="E28" t="n">
+        <v>43</v>
+      </c>
+      <c r="F28" t="n">
+        <v>510.1089655172414</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2633.401724137931</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>B0CF5TCQKL</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>7115</v>
+      </c>
+      <c r="E29" t="n">
+        <v>43</v>
+      </c>
+      <c r="F29" t="n">
+        <v>510.1089655172414</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2633.401724137931</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>B0CH4RT4P8</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>7115</v>
+      </c>
+      <c r="E30" t="n">
+        <v>43</v>
+      </c>
+      <c r="F30" t="n">
+        <v>510.1089655172414</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2633.401724137931</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>B0CKHVHVQ1</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>7115</v>
+      </c>
+      <c r="E31" t="n">
+        <v>43</v>
+      </c>
+      <c r="F31" t="n">
+        <v>510.1089655172414</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2633.401724137931</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>B0CM6NTWBP</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>7115</v>
+      </c>
+      <c r="E32" t="n">
+        <v>43</v>
+      </c>
+      <c r="F32" t="n">
+        <v>510.1089655172414</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2633.401724137931</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>B0D3M1B4Z8</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>7115</v>
+      </c>
+      <c r="E33" t="n">
+        <v>43</v>
+      </c>
+      <c r="F33" t="n">
+        <v>510.1089655172414</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2633.401724137931</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>B0DFMLS8JG</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>7115</v>
+      </c>
+      <c r="E34" t="n">
+        <v>43</v>
+      </c>
+      <c r="F34" t="n">
+        <v>510.1089655172414</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2633.401724137931</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>B0DFMMTWLY</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>7115</v>
+      </c>
+      <c r="E35" t="n">
+        <v>43</v>
+      </c>
+      <c r="F35" t="n">
+        <v>510.1089655172414</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2633.401724137931</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>B0DFMNGFTD</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>7115</v>
+      </c>
+      <c r="E36" t="n">
+        <v>43</v>
+      </c>
+      <c r="F36" t="n">
+        <v>510.1089655172414</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2633.401724137931</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
           <t>B0DT6T6N6B</t>
         </is>
       </c>
-      <c r="D23" t="n">
-        <v>2139</v>
-      </c>
-      <c r="E23" t="n">
-        <v>11</v>
-      </c>
-      <c r="F23" t="n">
-        <v>91.93880258425463</v>
-      </c>
-      <c r="G23" t="n">
-        <v>507.63</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="inlineStr">
+      <c r="D37" t="n">
+        <v>7115</v>
+      </c>
+      <c r="E37" t="n">
+        <v>43</v>
+      </c>
+      <c r="F37" t="n">
+        <v>510.1089655172414</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2633.401724137931</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>B0FF9R3GKK</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>7115</v>
+      </c>
+      <c r="E38" t="n">
+        <v>43</v>
+      </c>
+      <c r="F38" t="n">
+        <v>510.1089655172414</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2633.401724137931</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>B0G2C2RCXN</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>7115</v>
+      </c>
+      <c r="E39" t="n">
+        <v>43</v>
+      </c>
+      <c r="F39" t="n">
+        <v>510.1089655172414</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2633.401724137931</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>B0G3Q517Y2</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>7115</v>
+      </c>
+      <c r="E40" t="n">
+        <v>43</v>
+      </c>
+      <c r="F40" t="n">
+        <v>510.1089655172414</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2633.401724137931</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>B0G3Q59X8C</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>7115</v>
+      </c>
+      <c r="E41" t="n">
+        <v>43</v>
+      </c>
+      <c r="F41" t="n">
+        <v>510.1089655172414</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2633.401724137931</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>B0G4DNF8RZ</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>7115</v>
+      </c>
+      <c r="E42" t="n">
+        <v>43</v>
+      </c>
+      <c r="F42" t="n">
+        <v>510.1089655172414</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2633.401724137931</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" t="inlineStr">
         <is>
           <t>Audio Array</t>
         </is>

--- a/data/ams_weekly_data/Audio_Array/ads_report_week24.xlsx
+++ b/data/ams_weekly_data/Audio_Array/ads_report_week24.xlsx
@@ -1913,7 +1913,7 @@
         <v>99421.2</v>
       </c>
       <c r="H53" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="54">
@@ -14135,7 +14135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14198,19 +14198,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>27384</v>
+        <v>11163</v>
       </c>
       <c r="E2" t="n">
-        <v>153</v>
+        <v>62</v>
       </c>
       <c r="F2" t="n">
-        <v>2561.09</v>
+        <v>1044.066071787869</v>
       </c>
       <c r="G2" t="n">
-        <v>5506.780000000001</v>
+        <v>2244.92</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -14222,28 +14222,28 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Audio Array-B0BLJVJ2GN-AA 05 Suspension-SB-PT</t>
+          <t>Audio Array-B0B4DPX2J2-Condenser AM C1-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B0B4G8PH2P</t>
+          <t>B0CF5R3V95</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18658</v>
+        <v>16221</v>
       </c>
       <c r="E3" t="n">
-        <v>206</v>
+        <v>91</v>
       </c>
       <c r="F3" t="n">
-        <v>2778.746666666666</v>
+        <v>1517.023928212131</v>
       </c>
       <c r="G3" t="n">
-        <v>9951.690000000001</v>
+        <v>3261.86</v>
       </c>
       <c r="H3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -14260,23 +14260,23 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B0BLJVJ2GN</t>
+          <t>B0B4G8PH2P</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18658</v>
+        <v>14078</v>
       </c>
       <c r="E4" t="n">
-        <v>206</v>
+        <v>156</v>
       </c>
       <c r="F4" t="n">
-        <v>2778.746666666666</v>
+        <v>2096.581405689265</v>
       </c>
       <c r="G4" t="n">
-        <v>9951.690000000001</v>
+        <v>7508.611151736442</v>
       </c>
       <c r="H4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -14293,23 +14293,23 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B0CF5R3V95</t>
+          <t>B0BLJVJ2GN</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18658</v>
+        <v>14172</v>
       </c>
       <c r="E5" t="n">
-        <v>206</v>
+        <v>157</v>
       </c>
       <c r="F5" t="n">
-        <v>2778.746666666666</v>
+        <v>2110.564857215983</v>
       </c>
       <c r="G5" t="n">
-        <v>9951.690000000001</v>
+        <v>7558.690914815696</v>
       </c>
       <c r="H5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -14321,28 +14321,28 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Audio Array-B0BPLZ5CGV-AI 04 Audio Interface-SBV -PT</t>
+          <t>Audio Array-B0BLJVJ2GN-AA 05 Suspension-SB-PT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0CF5R3V95</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>82240</v>
+        <v>16810</v>
       </c>
       <c r="E6" t="n">
-        <v>621</v>
+        <v>186</v>
       </c>
       <c r="F6" t="n">
-        <v>5743.17</v>
+        <v>2503.406212784919</v>
       </c>
       <c r="G6" t="n">
-        <v>36602.54</v>
+        <v>8965.596926327536</v>
       </c>
       <c r="H6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -14354,25 +14354,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Audio Array-B0CKHVHVQ1-AM W45 Wireless-SBV-KT-Phrase</t>
+          <t>Audio Array-B0BLJVJ2GN-AA 05 Suspension-SB-PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0CKHVHVQ1</t>
+          <t>B0D3M86SH1</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>19575</v>
+        <v>10916</v>
       </c>
       <c r="E7" t="n">
-        <v>85</v>
+        <v>121</v>
       </c>
       <c r="F7" t="n">
-        <v>1245.08</v>
+        <v>1625.687524309833</v>
       </c>
       <c r="G7" t="n">
-        <v>17623.72</v>
+        <v>5822.171007120328</v>
       </c>
       <c r="H7" t="n">
         <v>4</v>
@@ -14387,28 +14387,28 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Audio Array-B0CKHVHVQ1-AM W45 Wireless-SBV-KT-Phrase (2)</t>
+          <t>Audio Array-B0BPLZ5CGV-AI 04 Audio Interface-SBV -PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0CKHVHVQ1</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>24091</v>
+        <v>82240</v>
       </c>
       <c r="E8" t="n">
-        <v>146</v>
+        <v>621</v>
       </c>
       <c r="F8" t="n">
-        <v>1053.12</v>
+        <v>5743.17</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>36602.54</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -14420,7 +14420,7 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Audio Array-B0CKHVHVQ1-AM W45 Wireless-SBV-PT</t>
+          <t>Audio Array-B0CKHVHVQ1-AM W45 Wireless-SBV-KT-Phrase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -14429,19 +14429,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>60085</v>
+        <v>19575</v>
       </c>
       <c r="E9" t="n">
-        <v>465</v>
+        <v>85</v>
       </c>
       <c r="F9" t="n">
-        <v>2410.22</v>
+        <v>1245.08</v>
       </c>
       <c r="G9" t="n">
-        <v>4405.93</v>
+        <v>17623.72</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -14453,22 +14453,22 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Audio Array-B0DXFPM4N2-Studio Monitor- SBV-CT</t>
+          <t>Audio Array-B0CKHVHVQ1-AM W45 Wireless-SBV-KT-Phrase (2)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B0DXFPM4N2</t>
+          <t>B0CKHVHVQ1</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>19117</v>
+        <v>24091</v>
       </c>
       <c r="E10" t="n">
-        <v>249</v>
+        <v>146</v>
       </c>
       <c r="F10" t="n">
-        <v>2475.71</v>
+        <v>1053.12</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -14486,28 +14486,28 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Audio Array-Catch All-Condenser -SB-PT</t>
+          <t>Audio Array-B0CKHVHVQ1-AM W45 Wireless-SBV-PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B0B4DPX2J2</t>
+          <t>B0CKHVHVQ1</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13680</v>
+        <v>60085</v>
       </c>
       <c r="E11" t="n">
-        <v>143</v>
+        <v>465</v>
       </c>
       <c r="F11" t="n">
-        <v>2123.736666666667</v>
+        <v>2410.22</v>
       </c>
       <c r="G11" t="n">
-        <v>5718.37</v>
+        <v>4405.93</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -14519,28 +14519,28 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Audio Array-Catch All-Condenser -SB-PT</t>
+          <t>Audio Array-B0DXFPM4N2-Studio Monitor- SBV-CT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B0D3M1B4Z8</t>
+          <t>B0DXFPM4N2</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13680</v>
+        <v>19117</v>
       </c>
       <c r="E12" t="n">
-        <v>143</v>
+        <v>249</v>
       </c>
       <c r="F12" t="n">
-        <v>2123.736666666667</v>
+        <v>2475.71</v>
       </c>
       <c r="G12" t="n">
-        <v>5718.37</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -14557,23 +14557,23 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B0FF9R3GKK</t>
+          <t>B0B4DPX2J2</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13680</v>
+        <v>21483</v>
       </c>
       <c r="E13" t="n">
-        <v>143</v>
+        <v>224</v>
       </c>
       <c r="F13" t="n">
-        <v>2123.736666666667</v>
+        <v>3334.949587195885</v>
       </c>
       <c r="G13" t="n">
-        <v>5718.37</v>
+        <v>8979.68</v>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -14585,28 +14585,28 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+          <t>Audio Array-Catch All-Condenser -SB-PT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0B4DPX2J2</t>
+          <t>B0D3M1B4Z8</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>7115</v>
+        <v>13782</v>
       </c>
       <c r="E14" t="n">
-        <v>43</v>
+        <v>144</v>
       </c>
       <c r="F14" t="n">
-        <v>510.1089655172414</v>
+        <v>2139.576384773983</v>
       </c>
       <c r="G14" t="n">
-        <v>2633.401724137931</v>
+        <v>5761.02</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -14618,25 +14618,25 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+          <t>Audio Array-Catch All-Condenser -SB-PT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0B4DS678Q</t>
+          <t>B0FF9R3GKK</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>7115</v>
+        <v>5776</v>
       </c>
       <c r="E15" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="F15" t="n">
-        <v>510.1089655172414</v>
+        <v>896.684028030132</v>
       </c>
       <c r="G15" t="n">
-        <v>2633.401724137931</v>
+        <v>2414.41</v>
       </c>
       <c r="H15" t="n">
         <v>1</v>
@@ -14656,23 +14656,23 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0B4G19R58</t>
+          <t>B0B4DPX2J2</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>7115</v>
+        <v>26126</v>
       </c>
       <c r="E16" t="n">
-        <v>43</v>
+        <v>136</v>
       </c>
       <c r="F16" t="n">
-        <v>510.1089655172414</v>
+        <v>2020.133718092619</v>
       </c>
       <c r="G16" t="n">
-        <v>2633.401724137931</v>
+        <v>6734.760000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -14689,23 +14689,23 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0B4G1PXWV</t>
+          <t>B0B4K87PR4</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>7115</v>
+        <v>28565</v>
       </c>
       <c r="E17" t="n">
-        <v>43</v>
+        <v>144</v>
       </c>
       <c r="F17" t="n">
-        <v>510.1089655172414</v>
+        <v>1227.582149132192</v>
       </c>
       <c r="G17" t="n">
-        <v>2633.401724137931</v>
+        <v>6777.959999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -14722,23 +14722,23 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0B4G89VQJ</t>
+          <t>B0BLJVJ2GN</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>7115</v>
+        <v>1153</v>
       </c>
       <c r="E18" t="n">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="F18" t="n">
-        <v>510.1089655172414</v>
+        <v>242.4426520898196</v>
       </c>
       <c r="G18" t="n">
-        <v>2633.401724137931</v>
+        <v>550</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -14755,23 +14755,23 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0B4JRQP22</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>7115</v>
+        <v>49181</v>
       </c>
       <c r="E19" t="n">
-        <v>43</v>
+        <v>372</v>
       </c>
       <c r="F19" t="n">
-        <v>510.1089655172414</v>
+        <v>4289.9</v>
       </c>
       <c r="G19" t="n">
-        <v>2633.401724137931</v>
+        <v>34780.52</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -14788,23 +14788,23 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0B4K87PR4</t>
+          <t>B0CF5TCQKL</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>7115</v>
+        <v>13566</v>
       </c>
       <c r="E20" t="n">
-        <v>43</v>
+        <v>149</v>
       </c>
       <c r="F20" t="n">
-        <v>510.1089655172414</v>
+        <v>2852.52734791018</v>
       </c>
       <c r="G20" t="n">
-        <v>2633.401724137931</v>
+        <v>6471.18</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -14821,23 +14821,23 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0B4KC7VBM</t>
+          <t>B0CKHVHVQ1</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>7115</v>
+        <v>74274</v>
       </c>
       <c r="E21" t="n">
-        <v>43</v>
+        <v>376</v>
       </c>
       <c r="F21" t="n">
-        <v>510.1089655172414</v>
+        <v>3191.899048283553</v>
       </c>
       <c r="G21" t="n">
-        <v>2633.401724137931</v>
+        <v>17623.72</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -14854,20 +14854,20 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0BLJVJ2GN</t>
+          <t>B0D3LZWTHV</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>7115</v>
+        <v>11339</v>
       </c>
       <c r="E22" t="n">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="F22" t="n">
-        <v>510.1089655172414</v>
+        <v>876.7362819073812</v>
       </c>
       <c r="G22" t="n">
-        <v>2633.401724137931</v>
+        <v>2922.88</v>
       </c>
       <c r="H22" t="n">
         <v>1</v>
@@ -14887,652 +14887,25 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0BLK8DNPD</t>
+          <t>B0DT6T6N6B</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>7115</v>
+        <v>2139</v>
       </c>
       <c r="E23" t="n">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="F23" t="n">
-        <v>510.1089655172414</v>
+        <v>91.93880258425463</v>
       </c>
       <c r="G23" t="n">
-        <v>2633.401724137931</v>
+        <v>507.63</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>B0BPLZ5CGV</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>7115</v>
-      </c>
-      <c r="E24" t="n">
-        <v>43</v>
-      </c>
-      <c r="F24" t="n">
-        <v>510.1089655172414</v>
-      </c>
-      <c r="G24" t="n">
-        <v>2633.401724137931</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>B0C4YTNJG7</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>7115</v>
-      </c>
-      <c r="E25" t="n">
-        <v>43</v>
-      </c>
-      <c r="F25" t="n">
-        <v>510.1089655172414</v>
-      </c>
-      <c r="G25" t="n">
-        <v>2633.401724137931</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>B0C539RBGL</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>7115</v>
-      </c>
-      <c r="E26" t="n">
-        <v>43</v>
-      </c>
-      <c r="F26" t="n">
-        <v>510.1089655172414</v>
-      </c>
-      <c r="G26" t="n">
-        <v>2633.401724137931</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>B0CF5R3V95</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>7115</v>
-      </c>
-      <c r="E27" t="n">
-        <v>43</v>
-      </c>
-      <c r="F27" t="n">
-        <v>510.1089655172414</v>
-      </c>
-      <c r="G27" t="n">
-        <v>2633.401724137931</v>
-      </c>
-      <c r="H27" t="n">
-        <v>1</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>B0CF5RRTDJ</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>7115</v>
-      </c>
-      <c r="E28" t="n">
-        <v>43</v>
-      </c>
-      <c r="F28" t="n">
-        <v>510.1089655172414</v>
-      </c>
-      <c r="G28" t="n">
-        <v>2633.401724137931</v>
-      </c>
-      <c r="H28" t="n">
-        <v>1</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>B0CF5TCQKL</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>7115</v>
-      </c>
-      <c r="E29" t="n">
-        <v>43</v>
-      </c>
-      <c r="F29" t="n">
-        <v>510.1089655172414</v>
-      </c>
-      <c r="G29" t="n">
-        <v>2633.401724137931</v>
-      </c>
-      <c r="H29" t="n">
-        <v>1</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>B0CH4RT4P8</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>7115</v>
-      </c>
-      <c r="E30" t="n">
-        <v>43</v>
-      </c>
-      <c r="F30" t="n">
-        <v>510.1089655172414</v>
-      </c>
-      <c r="G30" t="n">
-        <v>2633.401724137931</v>
-      </c>
-      <c r="H30" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>B0CKHVHVQ1</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>7115</v>
-      </c>
-      <c r="E31" t="n">
-        <v>43</v>
-      </c>
-      <c r="F31" t="n">
-        <v>510.1089655172414</v>
-      </c>
-      <c r="G31" t="n">
-        <v>2633.401724137931</v>
-      </c>
-      <c r="H31" t="n">
-        <v>1</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>B0CM6NTWBP</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>7115</v>
-      </c>
-      <c r="E32" t="n">
-        <v>43</v>
-      </c>
-      <c r="F32" t="n">
-        <v>510.1089655172414</v>
-      </c>
-      <c r="G32" t="n">
-        <v>2633.401724137931</v>
-      </c>
-      <c r="H32" t="n">
-        <v>1</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>B0D3M1B4Z8</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>7115</v>
-      </c>
-      <c r="E33" t="n">
-        <v>43</v>
-      </c>
-      <c r="F33" t="n">
-        <v>510.1089655172414</v>
-      </c>
-      <c r="G33" t="n">
-        <v>2633.401724137931</v>
-      </c>
-      <c r="H33" t="n">
-        <v>1</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>B0DFMLS8JG</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>7115</v>
-      </c>
-      <c r="E34" t="n">
-        <v>43</v>
-      </c>
-      <c r="F34" t="n">
-        <v>510.1089655172414</v>
-      </c>
-      <c r="G34" t="n">
-        <v>2633.401724137931</v>
-      </c>
-      <c r="H34" t="n">
-        <v>1</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>B0DFMMTWLY</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>7115</v>
-      </c>
-      <c r="E35" t="n">
-        <v>43</v>
-      </c>
-      <c r="F35" t="n">
-        <v>510.1089655172414</v>
-      </c>
-      <c r="G35" t="n">
-        <v>2633.401724137931</v>
-      </c>
-      <c r="H35" t="n">
-        <v>1</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>B0DFMNGFTD</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>7115</v>
-      </c>
-      <c r="E36" t="n">
-        <v>43</v>
-      </c>
-      <c r="F36" t="n">
-        <v>510.1089655172414</v>
-      </c>
-      <c r="G36" t="n">
-        <v>2633.401724137931</v>
-      </c>
-      <c r="H36" t="n">
-        <v>1</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>B0DT6T6N6B</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>7115</v>
-      </c>
-      <c r="E37" t="n">
-        <v>43</v>
-      </c>
-      <c r="F37" t="n">
-        <v>510.1089655172414</v>
-      </c>
-      <c r="G37" t="n">
-        <v>2633.401724137931</v>
-      </c>
-      <c r="H37" t="n">
-        <v>1</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>B0FF9R3GKK</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>7115</v>
-      </c>
-      <c r="E38" t="n">
-        <v>43</v>
-      </c>
-      <c r="F38" t="n">
-        <v>510.1089655172414</v>
-      </c>
-      <c r="G38" t="n">
-        <v>2633.401724137931</v>
-      </c>
-      <c r="H38" t="n">
-        <v>1</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>B0G2C2RCXN</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>7115</v>
-      </c>
-      <c r="E39" t="n">
-        <v>43</v>
-      </c>
-      <c r="F39" t="n">
-        <v>510.1089655172414</v>
-      </c>
-      <c r="G39" t="n">
-        <v>2633.401724137931</v>
-      </c>
-      <c r="H39" t="n">
-        <v>1</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>B0G3Q517Y2</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>7115</v>
-      </c>
-      <c r="E40" t="n">
-        <v>43</v>
-      </c>
-      <c r="F40" t="n">
-        <v>510.1089655172414</v>
-      </c>
-      <c r="G40" t="n">
-        <v>2633.401724137931</v>
-      </c>
-      <c r="H40" t="n">
-        <v>1</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>B0G3Q59X8C</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>7115</v>
-      </c>
-      <c r="E41" t="n">
-        <v>43</v>
-      </c>
-      <c r="F41" t="n">
-        <v>510.1089655172414</v>
-      </c>
-      <c r="G41" t="n">
-        <v>2633.401724137931</v>
-      </c>
-      <c r="H41" t="n">
-        <v>1</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>B0G4DNF8RZ</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>7115</v>
-      </c>
-      <c r="E42" t="n">
-        <v>43</v>
-      </c>
-      <c r="F42" t="n">
-        <v>510.1089655172414</v>
-      </c>
-      <c r="G42" t="n">
-        <v>2633.401724137931</v>
-      </c>
-      <c r="H42" t="n">
-        <v>1</v>
-      </c>
-      <c r="I42" t="inlineStr">
         <is>
           <t>Audio Array</t>
         </is>

--- a/data/ams_weekly_data/Audio_Array/ads_report_week24.xlsx
+++ b/data/ams_weekly_data/Audio_Array/ads_report_week24.xlsx
@@ -1350,10 +1350,10 @@
         <v>91667</v>
       </c>
       <c r="G33" t="n">
-        <v>79843.38</v>
+        <v>82088.3</v>
       </c>
       <c r="H33" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34">
@@ -5127,7 +5127,7 @@
         <v>6</v>
       </c>
       <c r="F168" t="n">
-        <v>6460</v>
+        <v>6459</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -6633,13 +6633,13 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>11922.93</v>
+        <v>11921.93</v>
       </c>
       <c r="E222" t="n">
-        <v>4305</v>
+        <v>4304</v>
       </c>
       <c r="F222" t="n">
-        <v>591782</v>
+        <v>591781</v>
       </c>
       <c r="G222" t="n">
         <v>24572.88</v>
@@ -7706,10 +7706,10 @@
         <v>16593</v>
       </c>
       <c r="G260" t="n">
-        <v>3301.7</v>
+        <v>5503.4</v>
       </c>
       <c r="H260" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="261">
@@ -9890,10 +9890,10 @@
         <v>793</v>
       </c>
       <c r="G338" t="n">
-        <v>1355.08</v>
+        <v>4150.84</v>
       </c>
       <c r="H338" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="339">
@@ -11038,10 +11038,10 @@
         <v>20946</v>
       </c>
       <c r="G379" t="n">
-        <v>5379.66</v>
+        <v>8048.299999999999</v>
       </c>
       <c r="H379" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="380">
@@ -13278,10 +13278,10 @@
         <v>100218</v>
       </c>
       <c r="G15" t="n">
-        <v>3163.61</v>
+        <v>4264.46</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -13611,7 +13611,7 @@
         <v>1787</v>
       </c>
       <c r="F27" t="n">
-        <v>446788</v>
+        <v>446787</v>
       </c>
       <c r="G27" t="n">
         <v>5931.36</v>
@@ -13947,7 +13947,7 @@
         <v>4401</v>
       </c>
       <c r="F39" t="n">
-        <v>1175051</v>
+        <v>1175048</v>
       </c>
       <c r="G39" t="n">
         <v>13048.3</v>

--- a/data/ams_weekly_data/Audio_Array/ads_report_week24.xlsx
+++ b/data/ams_weekly_data/Audio_Array/ads_report_week24.xlsx
@@ -479,7 +479,7 @@
         <v>49</v>
       </c>
       <c r="F2" t="n">
-        <v>12977</v>
+        <v>12971</v>
       </c>
       <c r="G2" t="n">
         <v>3261.86</v>
@@ -507,7 +507,7 @@
         <v>57</v>
       </c>
       <c r="F3" t="n">
-        <v>12381</v>
+        <v>12378</v>
       </c>
       <c r="G3" t="n">
         <v>3388.14</v>
@@ -535,7 +535,7 @@
         <v>64</v>
       </c>
       <c r="F4" t="n">
-        <v>14216</v>
+        <v>14215</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -678,10 +678,10 @@
         <v>37621</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>7033.05</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -843,7 +843,7 @@
         <v>56</v>
       </c>
       <c r="F15" t="n">
-        <v>2651</v>
+        <v>2649</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -899,7 +899,7 @@
         <v>103</v>
       </c>
       <c r="F17" t="n">
-        <v>16201</v>
+        <v>16200</v>
       </c>
       <c r="G17" t="n">
         <v>2626.27</v>
@@ -927,7 +927,7 @@
         <v>175</v>
       </c>
       <c r="F18" t="n">
-        <v>26596</v>
+        <v>26579</v>
       </c>
       <c r="G18" t="n">
         <v>5250.84</v>
@@ -983,7 +983,7 @@
         <v>219</v>
       </c>
       <c r="F20" t="n">
-        <v>29246</v>
+        <v>29223</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1039,7 +1039,7 @@
         <v>33</v>
       </c>
       <c r="F22" t="n">
-        <v>7228</v>
+        <v>7225</v>
       </c>
       <c r="G22" t="n">
         <v>4828.82</v>
@@ -1151,7 +1151,7 @@
         <v>303</v>
       </c>
       <c r="F26" t="n">
-        <v>31414</v>
+        <v>31412</v>
       </c>
       <c r="G26" t="n">
         <v>35283.96</v>
@@ -1207,7 +1207,7 @@
         <v>46</v>
       </c>
       <c r="F28" t="n">
-        <v>10787</v>
+        <v>10785</v>
       </c>
       <c r="G28" t="n">
         <v>4489.84</v>
@@ -1263,7 +1263,7 @@
         <v>155</v>
       </c>
       <c r="F30" t="n">
-        <v>10302</v>
+        <v>10298</v>
       </c>
       <c r="G30" t="n">
         <v>6734.76</v>
@@ -1291,7 +1291,7 @@
         <v>307</v>
       </c>
       <c r="F31" t="n">
-        <v>22787</v>
+        <v>22780</v>
       </c>
       <c r="G31" t="n">
         <v>60994.19</v>
@@ -1319,7 +1319,7 @@
         <v>79</v>
       </c>
       <c r="F32" t="n">
-        <v>9755</v>
+        <v>9753</v>
       </c>
       <c r="G32" t="n">
         <v>14105.1</v>
@@ -1347,13 +1347,13 @@
         <v>1241</v>
       </c>
       <c r="F33" t="n">
-        <v>91667</v>
+        <v>91658</v>
       </c>
       <c r="G33" t="n">
         <v>82088.3</v>
       </c>
       <c r="H33" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34">
@@ -1403,7 +1403,7 @@
         <v>87</v>
       </c>
       <c r="F35" t="n">
-        <v>21885</v>
+        <v>21883</v>
       </c>
       <c r="G35" t="n">
         <v>6438.98</v>
@@ -1487,7 +1487,7 @@
         <v>57</v>
       </c>
       <c r="F38" t="n">
-        <v>6466</v>
+        <v>6464</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1711,7 +1711,7 @@
         <v>54</v>
       </c>
       <c r="F46" t="n">
-        <v>6555</v>
+        <v>6552</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1739,7 +1739,7 @@
         <v>206</v>
       </c>
       <c r="F47" t="n">
-        <v>36072</v>
+        <v>36071</v>
       </c>
       <c r="G47" t="n">
         <v>4066.95</v>
@@ -1767,7 +1767,7 @@
         <v>141</v>
       </c>
       <c r="F48" t="n">
-        <v>9097</v>
+        <v>9095</v>
       </c>
       <c r="G48" t="n">
         <v>20351.7</v>
@@ -1823,7 +1823,7 @@
         <v>360</v>
       </c>
       <c r="F50" t="n">
-        <v>56005</v>
+        <v>55980</v>
       </c>
       <c r="G50" t="n">
         <v>28485.6</v>
@@ -1907,7 +1907,7 @@
         <v>968</v>
       </c>
       <c r="F53" t="n">
-        <v>120620</v>
+        <v>120547</v>
       </c>
       <c r="G53" t="n">
         <v>99421.2</v>
@@ -1935,7 +1935,7 @@
         <v>261</v>
       </c>
       <c r="F54" t="n">
-        <v>18409</v>
+        <v>18403</v>
       </c>
       <c r="G54" t="n">
         <v>32535.58</v>
@@ -2131,7 +2131,7 @@
         <v>241</v>
       </c>
       <c r="F61" t="n">
-        <v>46270</v>
+        <v>46269</v>
       </c>
       <c r="G61" t="n">
         <v>18933.07</v>
@@ -2187,7 +2187,7 @@
         <v>47</v>
       </c>
       <c r="F63" t="n">
-        <v>4192</v>
+        <v>4190</v>
       </c>
       <c r="G63" t="n">
         <v>4362.72</v>
@@ -2215,7 +2215,7 @@
         <v>151</v>
       </c>
       <c r="F64" t="n">
-        <v>24171</v>
+        <v>24169</v>
       </c>
       <c r="G64" t="n">
         <v>16623.72</v>
@@ -2271,7 +2271,7 @@
         <v>48</v>
       </c>
       <c r="F66" t="n">
-        <v>3722</v>
+        <v>3721</v>
       </c>
       <c r="G66" t="n">
         <v>30841.52</v>
@@ -2299,7 +2299,7 @@
         <v>52</v>
       </c>
       <c r="F67" t="n">
-        <v>5613</v>
+        <v>5600</v>
       </c>
       <c r="G67" t="n">
         <v>17623.72</v>
@@ -2327,7 +2327,7 @@
         <v>89</v>
       </c>
       <c r="F68" t="n">
-        <v>8978</v>
+        <v>8975</v>
       </c>
       <c r="G68" t="n">
         <v>26469.48</v>
@@ -2411,7 +2411,7 @@
         <v>403</v>
       </c>
       <c r="F71" t="n">
-        <v>75249</v>
+        <v>75238</v>
       </c>
       <c r="G71" t="n">
         <v>2626.27</v>
@@ -2495,7 +2495,7 @@
         <v>57</v>
       </c>
       <c r="F74" t="n">
-        <v>15422</v>
+        <v>15416</v>
       </c>
       <c r="G74" t="n">
         <v>2015.26</v>
@@ -2607,7 +2607,7 @@
         <v>17</v>
       </c>
       <c r="F78" t="n">
-        <v>2439</v>
+        <v>2438</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2691,7 +2691,7 @@
         <v>1082</v>
       </c>
       <c r="F81" t="n">
-        <v>122157</v>
+        <v>122156</v>
       </c>
       <c r="G81" t="n">
         <v>84312.7</v>
@@ -2719,7 +2719,7 @@
         <v>897</v>
       </c>
       <c r="F82" t="n">
-        <v>194770</v>
+        <v>194696</v>
       </c>
       <c r="G82" t="n">
         <v>11219.48</v>
@@ -2775,7 +2775,7 @@
         <v>165</v>
       </c>
       <c r="F84" t="n">
-        <v>14178</v>
+        <v>14176</v>
       </c>
       <c r="G84" t="n">
         <v>9757.639999999999</v>
@@ -2915,7 +2915,7 @@
         <v>103</v>
       </c>
       <c r="F89" t="n">
-        <v>19767</v>
+        <v>19765</v>
       </c>
       <c r="G89" t="n">
         <v>13427.96</v>
@@ -2943,7 +2943,7 @@
         <v>19</v>
       </c>
       <c r="F90" t="n">
-        <v>2152</v>
+        <v>2151</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2971,7 +2971,7 @@
         <v>616</v>
       </c>
       <c r="F91" t="n">
-        <v>66327</v>
+        <v>66270</v>
       </c>
       <c r="G91" t="n">
         <v>21000.84</v>
@@ -3027,7 +3027,7 @@
         <v>92</v>
       </c>
       <c r="F93" t="n">
-        <v>4784</v>
+        <v>4779</v>
       </c>
       <c r="G93" t="n">
         <v>6988.98</v>
@@ -3083,7 +3083,7 @@
         <v>1343</v>
       </c>
       <c r="F95" t="n">
-        <v>116388</v>
+        <v>116363</v>
       </c>
       <c r="G95" t="n">
         <v>119305.08</v>
@@ -3111,13 +3111,13 @@
         <v>677</v>
       </c>
       <c r="F96" t="n">
-        <v>30950</v>
+        <v>30942</v>
       </c>
       <c r="G96" t="n">
-        <v>67787.28</v>
+        <v>74142.36</v>
       </c>
       <c r="H96" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="97">
@@ -3139,7 +3139,7 @@
         <v>259</v>
       </c>
       <c r="F97" t="n">
-        <v>18322</v>
+        <v>18312</v>
       </c>
       <c r="G97" t="n">
         <v>5931.36</v>
@@ -3167,7 +3167,7 @@
         <v>321</v>
       </c>
       <c r="F98" t="n">
-        <v>33375</v>
+        <v>33367</v>
       </c>
       <c r="G98" t="n">
         <v>5930.509999999999</v>
@@ -3223,7 +3223,7 @@
         <v>131</v>
       </c>
       <c r="F100" t="n">
-        <v>13719</v>
+        <v>13714</v>
       </c>
       <c r="G100" t="n">
         <v>13980.5</v>
@@ -3369,7 +3369,7 @@
         <v>11649.15</v>
       </c>
       <c r="H105" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106">
@@ -3643,7 +3643,7 @@
         <v>102</v>
       </c>
       <c r="F115" t="n">
-        <v>21611</v>
+        <v>21606</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3755,7 +3755,7 @@
         <v>46</v>
       </c>
       <c r="F119" t="n">
-        <v>7781</v>
+        <v>7780</v>
       </c>
       <c r="G119" t="n">
         <v>3981.36</v>
@@ -3783,7 +3783,7 @@
         <v>124</v>
       </c>
       <c r="F120" t="n">
-        <v>29314</v>
+        <v>29303</v>
       </c>
       <c r="G120" t="n">
         <v>4065.24</v>
@@ -4203,7 +4203,7 @@
         <v>111</v>
       </c>
       <c r="F135" t="n">
-        <v>50201</v>
+        <v>50200</v>
       </c>
       <c r="G135" t="n">
         <v>7370.35</v>
@@ -4371,7 +4371,7 @@
         <v>52</v>
       </c>
       <c r="F141" t="n">
-        <v>7843</v>
+        <v>7842</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4483,7 +4483,7 @@
         <v>91</v>
       </c>
       <c r="F145" t="n">
-        <v>18501</v>
+        <v>18500</v>
       </c>
       <c r="G145" t="n">
         <v>1523.73</v>
@@ -4539,7 +4539,7 @@
         <v>2001</v>
       </c>
       <c r="F147" t="n">
-        <v>184410</v>
+        <v>184408</v>
       </c>
       <c r="G147" t="n">
         <v>16096.62</v>
@@ -4710,10 +4710,10 @@
         <v>191806</v>
       </c>
       <c r="G153" t="n">
-        <v>21348.31</v>
+        <v>25415.26</v>
       </c>
       <c r="H153" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="154">
@@ -4791,7 +4791,7 @@
         <v>31</v>
       </c>
       <c r="F156" t="n">
-        <v>3841</v>
+        <v>3840</v>
       </c>
       <c r="G156" t="n">
         <v>5464.41</v>
@@ -5071,7 +5071,7 @@
         <v>283</v>
       </c>
       <c r="F166" t="n">
-        <v>58847</v>
+        <v>58846</v>
       </c>
       <c r="G166" t="n">
         <v>9825.42</v>
@@ -5379,7 +5379,7 @@
         <v>46</v>
       </c>
       <c r="F177" t="n">
-        <v>6977</v>
+        <v>6976</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5631,7 +5631,7 @@
         <v>436</v>
       </c>
       <c r="F186" t="n">
-        <v>93819</v>
+        <v>93817</v>
       </c>
       <c r="G186" t="n">
         <v>6138.97</v>
@@ -5659,7 +5659,7 @@
         <v>306</v>
       </c>
       <c r="F187" t="n">
-        <v>70012</v>
+        <v>70011</v>
       </c>
       <c r="G187" t="n">
         <v>14062.72</v>
@@ -5687,7 +5687,7 @@
         <v>7</v>
       </c>
       <c r="F188" t="n">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5799,7 +5799,7 @@
         <v>62</v>
       </c>
       <c r="F192" t="n">
-        <v>8581</v>
+        <v>8580</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -6191,13 +6191,13 @@
         <v>332</v>
       </c>
       <c r="F206" t="n">
-        <v>33381</v>
+        <v>33380</v>
       </c>
       <c r="G206" t="n">
-        <v>33850</v>
+        <v>31181.36</v>
       </c>
       <c r="H206" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="207">
@@ -6443,7 +6443,7 @@
         <v>2281</v>
       </c>
       <c r="F215" t="n">
-        <v>346556</v>
+        <v>346553</v>
       </c>
       <c r="G215" t="n">
         <v>9572.029999999999</v>
@@ -6471,7 +6471,7 @@
         <v>330</v>
       </c>
       <c r="F216" t="n">
-        <v>33908</v>
+        <v>33907</v>
       </c>
       <c r="G216" t="n">
         <v>10166.95</v>
@@ -6639,7 +6639,7 @@
         <v>4304</v>
       </c>
       <c r="F222" t="n">
-        <v>591781</v>
+        <v>591778</v>
       </c>
       <c r="G222" t="n">
         <v>24572.88</v>
@@ -6667,7 +6667,7 @@
         <v>559</v>
       </c>
       <c r="F223" t="n">
-        <v>75825</v>
+        <v>75824</v>
       </c>
       <c r="G223" t="n">
         <v>15252.54</v>
@@ -6835,7 +6835,7 @@
         <v>149</v>
       </c>
       <c r="F229" t="n">
-        <v>28742</v>
+        <v>28710</v>
       </c>
       <c r="G229" t="n">
         <v>26692.37</v>
@@ -6863,7 +6863,7 @@
         <v>354</v>
       </c>
       <c r="F230" t="n">
-        <v>38631</v>
+        <v>38620</v>
       </c>
       <c r="G230" t="n">
         <v>12286.44</v>
@@ -6891,7 +6891,7 @@
         <v>48</v>
       </c>
       <c r="F231" t="n">
-        <v>8535</v>
+        <v>8522</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6919,7 +6919,7 @@
         <v>115</v>
       </c>
       <c r="F232" t="n">
-        <v>12085</v>
+        <v>12070</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6947,7 +6947,7 @@
         <v>733</v>
       </c>
       <c r="F233" t="n">
-        <v>27844</v>
+        <v>27836</v>
       </c>
       <c r="G233" t="n">
         <v>41976.25</v>
@@ -6975,7 +6975,7 @@
         <v>498</v>
       </c>
       <c r="F234" t="n">
-        <v>27247</v>
+        <v>27236</v>
       </c>
       <c r="G234" t="n">
         <v>40711.87</v>
@@ -7003,7 +7003,7 @@
         <v>515</v>
       </c>
       <c r="F235" t="n">
-        <v>46811</v>
+        <v>46804</v>
       </c>
       <c r="G235" t="n">
         <v>14066.1</v>
@@ -7031,7 +7031,7 @@
         <v>243</v>
       </c>
       <c r="F236" t="n">
-        <v>33810</v>
+        <v>33804</v>
       </c>
       <c r="G236" t="n">
         <v>16100</v>
@@ -7087,7 +7087,7 @@
         <v>168</v>
       </c>
       <c r="F238" t="n">
-        <v>12391</v>
+        <v>12388</v>
       </c>
       <c r="G238" t="n">
         <v>7033.05</v>
@@ -7115,7 +7115,7 @@
         <v>44</v>
       </c>
       <c r="F239" t="n">
-        <v>4373</v>
+        <v>4369</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -7339,7 +7339,7 @@
         <v>588</v>
       </c>
       <c r="F247" t="n">
-        <v>47373</v>
+        <v>47358</v>
       </c>
       <c r="G247" t="n">
         <v>68492.49000000001</v>
@@ -7423,7 +7423,7 @@
         <v>104</v>
       </c>
       <c r="F250" t="n">
-        <v>9986</v>
+        <v>9981</v>
       </c>
       <c r="G250" t="n">
         <v>5082.21</v>
@@ -7563,7 +7563,7 @@
         <v>18</v>
       </c>
       <c r="F255" t="n">
-        <v>4606</v>
+        <v>4602</v>
       </c>
       <c r="G255" t="n">
         <v>0</v>
@@ -7647,7 +7647,7 @@
         <v>59</v>
       </c>
       <c r="F258" t="n">
-        <v>15767</v>
+        <v>15763</v>
       </c>
       <c r="G258" t="n">
         <v>3879.71</v>
@@ -7703,7 +7703,7 @@
         <v>99</v>
       </c>
       <c r="F260" t="n">
-        <v>16593</v>
+        <v>16592</v>
       </c>
       <c r="G260" t="n">
         <v>5503.4</v>
@@ -7871,7 +7871,7 @@
         <v>26</v>
       </c>
       <c r="F266" t="n">
-        <v>5519</v>
+        <v>5518</v>
       </c>
       <c r="G266" t="n">
         <v>2075.42</v>
@@ -7983,7 +7983,7 @@
         <v>378</v>
       </c>
       <c r="F270" t="n">
-        <v>59463</v>
+        <v>59457</v>
       </c>
       <c r="G270" t="n">
         <v>16940.69</v>
@@ -8067,7 +8067,7 @@
         <v>96</v>
       </c>
       <c r="F273" t="n">
-        <v>26997</v>
+        <v>26996</v>
       </c>
       <c r="G273" t="n">
         <v>12200</v>
@@ -8095,7 +8095,7 @@
         <v>23</v>
       </c>
       <c r="F274" t="n">
-        <v>2651</v>
+        <v>2650</v>
       </c>
       <c r="G274" t="n">
         <v>0</v>
@@ -8123,7 +8123,7 @@
         <v>236</v>
       </c>
       <c r="F275" t="n">
-        <v>38831</v>
+        <v>38810</v>
       </c>
       <c r="G275" t="n">
         <v>5379.66</v>
@@ -8151,7 +8151,7 @@
         <v>53</v>
       </c>
       <c r="F276" t="n">
-        <v>10764</v>
+        <v>10763</v>
       </c>
       <c r="G276" t="n">
         <v>1007.63</v>
@@ -8179,7 +8179,7 @@
         <v>64</v>
       </c>
       <c r="F277" t="n">
-        <v>15728</v>
+        <v>15726</v>
       </c>
       <c r="G277" t="n">
         <v>5038.15</v>
@@ -8207,7 +8207,7 @@
         <v>349</v>
       </c>
       <c r="F278" t="n">
-        <v>49060</v>
+        <v>49054</v>
       </c>
       <c r="G278" t="n">
         <v>24053.33</v>
@@ -8235,7 +8235,7 @@
         <v>94</v>
       </c>
       <c r="F279" t="n">
-        <v>9747</v>
+        <v>9743</v>
       </c>
       <c r="G279" t="n">
         <v>0</v>
@@ -8263,7 +8263,7 @@
         <v>91</v>
       </c>
       <c r="F280" t="n">
-        <v>12394</v>
+        <v>12386</v>
       </c>
       <c r="G280" t="n">
         <v>13555.07</v>
@@ -8291,7 +8291,7 @@
         <v>232</v>
       </c>
       <c r="F281" t="n">
-        <v>39810</v>
+        <v>39782</v>
       </c>
       <c r="G281" t="n">
         <v>14136.44</v>
@@ -8319,7 +8319,7 @@
         <v>896</v>
       </c>
       <c r="F282" t="n">
-        <v>133754</v>
+        <v>133745</v>
       </c>
       <c r="G282" t="n">
         <v>43289.07</v>
@@ -8347,7 +8347,7 @@
         <v>49</v>
       </c>
       <c r="F283" t="n">
-        <v>4007</v>
+        <v>4002</v>
       </c>
       <c r="G283" t="n">
         <v>1395.75</v>
@@ -8375,7 +8375,7 @@
         <v>99</v>
       </c>
       <c r="F284" t="n">
-        <v>19730</v>
+        <v>19729</v>
       </c>
       <c r="G284" t="n">
         <v>2880.51</v>
@@ -8403,7 +8403,7 @@
         <v>766</v>
       </c>
       <c r="F285" t="n">
-        <v>260664</v>
+        <v>260648</v>
       </c>
       <c r="G285" t="n">
         <v>5122.87</v>
@@ -8459,7 +8459,7 @@
         <v>686</v>
       </c>
       <c r="F287" t="n">
-        <v>170460</v>
+        <v>170451</v>
       </c>
       <c r="G287" t="n">
         <v>8171.18</v>
@@ -8683,7 +8683,7 @@
         <v>81</v>
       </c>
       <c r="F295" t="n">
-        <v>10376</v>
+        <v>10372</v>
       </c>
       <c r="G295" t="n">
         <v>15760.17</v>
@@ -9019,7 +9019,7 @@
         <v>66</v>
       </c>
       <c r="F307" t="n">
-        <v>10151</v>
+        <v>10149</v>
       </c>
       <c r="G307" t="n">
         <v>7880.51</v>
@@ -9103,13 +9103,13 @@
         <v>393</v>
       </c>
       <c r="F310" t="n">
-        <v>45464</v>
+        <v>45462</v>
       </c>
       <c r="G310" t="n">
         <v>35584.75</v>
       </c>
       <c r="H310" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="311">
@@ -9131,13 +9131,13 @@
         <v>851</v>
       </c>
       <c r="F311" t="n">
-        <v>83500</v>
+        <v>83491</v>
       </c>
       <c r="G311" t="n">
-        <v>36126.26</v>
+        <v>38455.92</v>
       </c>
       <c r="H311" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="312">
@@ -9243,7 +9243,7 @@
         <v>13</v>
       </c>
       <c r="F315" t="n">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="G315" t="n">
         <v>0</v>
@@ -9383,7 +9383,7 @@
         <v>31</v>
       </c>
       <c r="F320" t="n">
-        <v>3303</v>
+        <v>3300</v>
       </c>
       <c r="G320" t="n">
         <v>2201.7</v>
@@ -9439,7 +9439,7 @@
         <v>57</v>
       </c>
       <c r="F322" t="n">
-        <v>8493</v>
+        <v>8490</v>
       </c>
       <c r="G322" t="n">
         <v>3219.49</v>
@@ -9523,7 +9523,7 @@
         <v>27</v>
       </c>
       <c r="F325" t="n">
-        <v>3821</v>
+        <v>3820</v>
       </c>
       <c r="G325" t="n">
         <v>10970.36</v>
@@ -9551,7 +9551,7 @@
         <v>283</v>
       </c>
       <c r="F326" t="n">
-        <v>23897</v>
+        <v>23893</v>
       </c>
       <c r="G326" t="n">
         <v>9743.219999999999</v>
@@ -9663,7 +9663,7 @@
         <v>85</v>
       </c>
       <c r="F330" t="n">
-        <v>17915</v>
+        <v>17912</v>
       </c>
       <c r="G330" t="n">
         <v>9319.49</v>
@@ -9691,7 +9691,7 @@
         <v>229</v>
       </c>
       <c r="F331" t="n">
-        <v>27188</v>
+        <v>27187</v>
       </c>
       <c r="G331" t="n">
         <v>11094.9</v>
@@ -9915,7 +9915,7 @@
         <v>13</v>
       </c>
       <c r="F339" t="n">
-        <v>2381</v>
+        <v>2380</v>
       </c>
       <c r="G339" t="n">
         <v>3261.86</v>
@@ -10195,7 +10195,7 @@
         <v>262</v>
       </c>
       <c r="F349" t="n">
-        <v>22869</v>
+        <v>22868</v>
       </c>
       <c r="G349" t="n">
         <v>6609.360000000001</v>
@@ -10363,7 +10363,7 @@
         <v>9</v>
       </c>
       <c r="F355" t="n">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="G355" t="n">
         <v>0</v>
@@ -10419,7 +10419,7 @@
         <v>114</v>
       </c>
       <c r="F357" t="n">
-        <v>17817</v>
+        <v>17816</v>
       </c>
       <c r="G357" t="n">
         <v>3942.48</v>
@@ -10559,7 +10559,7 @@
         <v>22</v>
       </c>
       <c r="F362" t="n">
-        <v>2334</v>
+        <v>2333</v>
       </c>
       <c r="G362" t="n">
         <v>0</v>
@@ -10699,7 +10699,7 @@
         <v>94</v>
       </c>
       <c r="F367" t="n">
-        <v>11816</v>
+        <v>11814</v>
       </c>
       <c r="G367" t="n">
         <v>1397.46</v>
@@ -10727,7 +10727,7 @@
         <v>223</v>
       </c>
       <c r="F368" t="n">
-        <v>21089</v>
+        <v>21085</v>
       </c>
       <c r="G368" t="n">
         <v>0</v>
@@ -11063,7 +11063,7 @@
         <v>183</v>
       </c>
       <c r="F380" t="n">
-        <v>17024</v>
+        <v>17023</v>
       </c>
       <c r="G380" t="n">
         <v>42324.59</v>
@@ -11259,7 +11259,7 @@
         <v>13</v>
       </c>
       <c r="F387" t="n">
-        <v>2839</v>
+        <v>2838</v>
       </c>
       <c r="G387" t="n">
         <v>0</v>
@@ -11293,7 +11293,7 @@
         <v>5641.96</v>
       </c>
       <c r="H388" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="389">
@@ -11315,7 +11315,7 @@
         <v>455</v>
       </c>
       <c r="F389" t="n">
-        <v>45906</v>
+        <v>45904</v>
       </c>
       <c r="G389" t="n">
         <v>19357.62</v>
@@ -11343,7 +11343,7 @@
         <v>787</v>
       </c>
       <c r="F390" t="n">
-        <v>60191</v>
+        <v>60186</v>
       </c>
       <c r="G390" t="n">
         <v>12286.44</v>
@@ -11455,7 +11455,7 @@
         <v>117</v>
       </c>
       <c r="F394" t="n">
-        <v>19671</v>
+        <v>19669</v>
       </c>
       <c r="G394" t="n">
         <v>2117.8</v>
@@ -11483,7 +11483,7 @@
         <v>243</v>
       </c>
       <c r="F395" t="n">
-        <v>28228</v>
+        <v>28225</v>
       </c>
       <c r="G395" t="n">
         <v>0</v>
@@ -11539,7 +11539,7 @@
         <v>55</v>
       </c>
       <c r="F397" t="n">
-        <v>10311</v>
+        <v>10310</v>
       </c>
       <c r="G397" t="n">
         <v>0</v>
@@ -11651,7 +11651,7 @@
         <v>91</v>
       </c>
       <c r="F401" t="n">
-        <v>11108</v>
+        <v>11106</v>
       </c>
       <c r="G401" t="n">
         <v>4236.44</v>
@@ -12071,7 +12071,7 @@
         <v>349</v>
       </c>
       <c r="F416" t="n">
-        <v>32180</v>
+        <v>32177</v>
       </c>
       <c r="G416" t="n">
         <v>24494.5</v>
@@ -12155,7 +12155,7 @@
         <v>138</v>
       </c>
       <c r="F419" t="n">
-        <v>24366</v>
+        <v>24364</v>
       </c>
       <c r="G419" t="n">
         <v>11861.02</v>
@@ -12183,7 +12183,7 @@
         <v>163</v>
       </c>
       <c r="F420" t="n">
-        <v>23711</v>
+        <v>23704</v>
       </c>
       <c r="G420" t="n">
         <v>15246.62</v>
@@ -12211,7 +12211,7 @@
         <v>186</v>
       </c>
       <c r="F421" t="n">
-        <v>34716</v>
+        <v>34715</v>
       </c>
       <c r="G421" t="n">
         <v>13508.37</v>
@@ -12239,7 +12239,7 @@
         <v>56</v>
       </c>
       <c r="F422" t="n">
-        <v>10464</v>
+        <v>10463</v>
       </c>
       <c r="G422" t="n">
         <v>0</v>
@@ -12323,7 +12323,7 @@
         <v>162</v>
       </c>
       <c r="F425" t="n">
-        <v>44755</v>
+        <v>44750</v>
       </c>
       <c r="G425" t="n">
         <v>3388.14</v>
@@ -12379,7 +12379,7 @@
         <v>72</v>
       </c>
       <c r="F427" t="n">
-        <v>14163</v>
+        <v>14162</v>
       </c>
       <c r="G427" t="n">
         <v>9148.309999999999</v>
@@ -12407,7 +12407,7 @@
         <v>89</v>
       </c>
       <c r="F428" t="n">
-        <v>16363</v>
+        <v>16360</v>
       </c>
       <c r="G428" t="n">
         <v>0</v>
@@ -12435,7 +12435,7 @@
         <v>14</v>
       </c>
       <c r="F429" t="n">
-        <v>8309</v>
+        <v>8308</v>
       </c>
       <c r="G429" t="n">
         <v>0</v>
@@ -12463,7 +12463,7 @@
         <v>40</v>
       </c>
       <c r="F430" t="n">
-        <v>14167</v>
+        <v>14166</v>
       </c>
       <c r="G430" t="n">
         <v>0</v>
@@ -12659,7 +12659,7 @@
         <v>57</v>
       </c>
       <c r="F437" t="n">
-        <v>10566</v>
+        <v>10565</v>
       </c>
       <c r="G437" t="n">
         <v>7370.34</v>
@@ -12687,7 +12687,7 @@
         <v>7</v>
       </c>
       <c r="F438" t="n">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="G438" t="n">
         <v>0</v>
@@ -12771,7 +12771,7 @@
         <v>99</v>
       </c>
       <c r="F441" t="n">
-        <v>28591</v>
+        <v>28590</v>
       </c>
       <c r="G441" t="n">
         <v>3195.73</v>
@@ -12799,7 +12799,7 @@
         <v>44</v>
       </c>
       <c r="F442" t="n">
-        <v>19186</v>
+        <v>19182</v>
       </c>
       <c r="G442" t="n">
         <v>4616.950000000001</v>
@@ -13026,10 +13026,10 @@
         <v>82055</v>
       </c>
       <c r="G6" t="n">
-        <v>16940.7</v>
+        <v>18634.77</v>
       </c>
       <c r="H6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -13325,10 +13325,10 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>460.16</v>
+        <v>458.15</v>
       </c>
       <c r="E17" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F17" t="n">
         <v>35261</v>
@@ -13530,10 +13530,10 @@
         <v>20885</v>
       </c>
       <c r="G24" t="n">
-        <v>9149.16</v>
+        <v>10843.23</v>
       </c>
       <c r="H24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -13605,13 +13605,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>4479.12</v>
+        <v>4476.28</v>
       </c>
       <c r="E27" t="n">
-        <v>1787</v>
+        <v>1785</v>
       </c>
       <c r="F27" t="n">
-        <v>446787</v>
+        <v>446785</v>
       </c>
       <c r="G27" t="n">
         <v>5931.36</v>
@@ -13807,7 +13807,7 @@
         <v>661</v>
       </c>
       <c r="F34" t="n">
-        <v>157623</v>
+        <v>157621</v>
       </c>
       <c r="G34" t="n">
         <v>2329.66</v>
@@ -13866,10 +13866,10 @@
         <v>19673</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>3982.2</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -13941,13 +13941,13 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>8063.92</v>
+        <v>8058.63</v>
       </c>
       <c r="E39" t="n">
-        <v>4401</v>
+        <v>4396</v>
       </c>
       <c r="F39" t="n">
-        <v>1175048</v>
+        <v>1175042</v>
       </c>
       <c r="G39" t="n">
         <v>13048.3</v>

--- a/data/ams_weekly_data/Audio_Array/ads_report_week24.xlsx
+++ b/data/ams_weekly_data/Audio_Array/ads_report_week24.xlsx
@@ -14231,7 +14231,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16221</v>
+        <v>16220</v>
       </c>
       <c r="E3" t="n">
         <v>91</v>
@@ -14396,13 +14396,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>82240</v>
+        <v>82230</v>
       </c>
       <c r="E8" t="n">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="F8" t="n">
-        <v>5743.17</v>
+        <v>5717.33</v>
       </c>
       <c r="G8" t="n">
         <v>36602.54</v>
@@ -14429,7 +14429,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>19575</v>
+        <v>19568</v>
       </c>
       <c r="E9" t="n">
         <v>85</v>
@@ -14462,7 +14462,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>24091</v>
+        <v>24086</v>
       </c>
       <c r="E10" t="n">
         <v>146</v>
@@ -14495,7 +14495,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>60085</v>
+        <v>60083</v>
       </c>
       <c r="E11" t="n">
         <v>465</v>
@@ -14660,7 +14660,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>26126</v>
+        <v>26124</v>
       </c>
       <c r="E16" t="n">
         <v>136</v>
@@ -14759,7 +14759,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>49181</v>
+        <v>49179</v>
       </c>
       <c r="E19" t="n">
         <v>372</v>
@@ -14768,10 +14768,10 @@
         <v>4289.9</v>
       </c>
       <c r="G19" t="n">
-        <v>34780.52</v>
+        <v>30713.57</v>
       </c>
       <c r="H19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -14825,7 +14825,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>74274</v>
+        <v>74272</v>
       </c>
       <c r="E21" t="n">
         <v>376</v>
@@ -14858,7 +14858,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11339</v>
+        <v>11338</v>
       </c>
       <c r="E22" t="n">
         <v>59</v>

--- a/data/ams_weekly_data/Audio_Array/ads_report_week24.xlsx
+++ b/data/ams_weekly_data/Audio_Array/ads_report_week24.xlsx
@@ -3226,10 +3226,10 @@
         <v>13714</v>
       </c>
       <c r="G100" t="n">
-        <v>13980.5</v>
+        <v>18640.67</v>
       </c>
       <c r="H100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="101">
@@ -7989,7 +7989,7 @@
         <v>16940.69</v>
       </c>
       <c r="H270" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="271">
@@ -13222,10 +13222,10 @@
         <v>166237</v>
       </c>
       <c r="G13" t="n">
-        <v>41559.32</v>
+        <v>45626.27</v>
       </c>
       <c r="H13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">

--- a/data/ams_weekly_data/Audio_Array/ads_report_week24.xlsx
+++ b/data/ams_weekly_data/Audio_Array/ads_report_week24.xlsx
@@ -2187,7 +2187,7 @@
         <v>47</v>
       </c>
       <c r="F63" t="n">
-        <v>4190</v>
+        <v>4189</v>
       </c>
       <c r="G63" t="n">
         <v>4362.72</v>
@@ -2691,7 +2691,7 @@
         <v>1082</v>
       </c>
       <c r="F81" t="n">
-        <v>122156</v>
+        <v>122154</v>
       </c>
       <c r="G81" t="n">
         <v>84312.7</v>
@@ -3077,13 +3077,13 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>13269.73</v>
+        <v>13264.83</v>
       </c>
       <c r="E95" t="n">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="F95" t="n">
-        <v>116363</v>
+        <v>116361</v>
       </c>
       <c r="G95" t="n">
         <v>119305.08</v>
@@ -3559,7 +3559,7 @@
         <v>59</v>
       </c>
       <c r="F112" t="n">
-        <v>8295</v>
+        <v>8294</v>
       </c>
       <c r="G112" t="n">
         <v>16309.3</v>
@@ -4595,7 +4595,7 @@
         <v>12</v>
       </c>
       <c r="F149" t="n">
-        <v>5488</v>
+        <v>5486</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -6639,7 +6639,7 @@
         <v>4304</v>
       </c>
       <c r="F222" t="n">
-        <v>591778</v>
+        <v>591776</v>
       </c>
       <c r="G222" t="n">
         <v>24572.88</v>
@@ -7703,7 +7703,7 @@
         <v>99</v>
       </c>
       <c r="F260" t="n">
-        <v>16592</v>
+        <v>16591</v>
       </c>
       <c r="G260" t="n">
         <v>5503.4</v>
@@ -8313,13 +8313,13 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>11065.31</v>
+        <v>11055.96</v>
       </c>
       <c r="E282" t="n">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="F282" t="n">
-        <v>133745</v>
+        <v>133743</v>
       </c>
       <c r="G282" t="n">
         <v>43289.07</v>
@@ -13611,7 +13611,7 @@
         <v>1785</v>
       </c>
       <c r="F27" t="n">
-        <v>446785</v>
+        <v>446784</v>
       </c>
       <c r="G27" t="n">
         <v>5931.36</v>
@@ -13941,13 +13941,13 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>8058.63</v>
+        <v>8056.24</v>
       </c>
       <c r="E39" t="n">
-        <v>4396</v>
+        <v>4394</v>
       </c>
       <c r="F39" t="n">
-        <v>1175042</v>
+        <v>1175036</v>
       </c>
       <c r="G39" t="n">
         <v>13048.3</v>

--- a/data/ams_weekly_data/Audio_Array/ads_report_week24.xlsx
+++ b/data/ams_weekly_data/Audio_Array/ads_report_week24.xlsx
@@ -2719,7 +2719,7 @@
         <v>897</v>
       </c>
       <c r="F82" t="n">
-        <v>194696</v>
+        <v>194695</v>
       </c>
       <c r="G82" t="n">
         <v>11219.48</v>
@@ -13947,7 +13947,7 @@
         <v>4394</v>
       </c>
       <c r="F39" t="n">
-        <v>1175036</v>
+        <v>1175035</v>
       </c>
       <c r="G39" t="n">
         <v>13048.3</v>
@@ -14135,7 +14135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14198,19 +14198,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11163</v>
+        <v>27383</v>
       </c>
       <c r="E2" t="n">
-        <v>62</v>
+        <v>153</v>
       </c>
       <c r="F2" t="n">
-        <v>1044.066071787869</v>
+        <v>2561.09</v>
       </c>
       <c r="G2" t="n">
-        <v>2244.92</v>
+        <v>5506.780000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -14222,28 +14222,28 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Audio Array-B0B4DPX2J2-Condenser AM C1-SBV-KT-Exact/Phrase</t>
+          <t>Audio Array-B0BLJVJ2GN-AA 05 Suspension-SB-PT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B0CF5R3V95</t>
+          <t>B0B4G8PH2P</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16220</v>
+        <v>18658</v>
       </c>
       <c r="E3" t="n">
-        <v>91</v>
+        <v>206</v>
       </c>
       <c r="F3" t="n">
-        <v>1517.023928212131</v>
+        <v>2778.746666666666</v>
       </c>
       <c r="G3" t="n">
-        <v>3261.86</v>
+        <v>9951.690000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -14260,23 +14260,23 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B0B4G8PH2P</t>
+          <t>B0BLJVJ2GN</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14078</v>
+        <v>18658</v>
       </c>
       <c r="E4" t="n">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="F4" t="n">
-        <v>2096.581405689265</v>
+        <v>2778.746666666666</v>
       </c>
       <c r="G4" t="n">
-        <v>7508.611151736442</v>
+        <v>9951.690000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -14293,23 +14293,23 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B0BLJVJ2GN</t>
+          <t>B0CF5R3V95</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14172</v>
+        <v>18658</v>
       </c>
       <c r="E5" t="n">
-        <v>157</v>
+        <v>206</v>
       </c>
       <c r="F5" t="n">
-        <v>2110.564857215983</v>
+        <v>2778.746666666666</v>
       </c>
       <c r="G5" t="n">
-        <v>7558.690914815696</v>
+        <v>9951.690000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -14321,28 +14321,28 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Audio Array-B0BLJVJ2GN-AA 05 Suspension-SB-PT</t>
+          <t>Audio Array-B0BPLZ5CGV-AI 04 Audio Interface-SBV -PT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B0CF5R3V95</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16810</v>
+        <v>82230</v>
       </c>
       <c r="E6" t="n">
-        <v>186</v>
+        <v>620</v>
       </c>
       <c r="F6" t="n">
-        <v>2503.406212784919</v>
+        <v>5717.33</v>
       </c>
       <c r="G6" t="n">
-        <v>8965.596926327536</v>
+        <v>36602.54</v>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -14354,25 +14354,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Audio Array-B0BLJVJ2GN-AA 05 Suspension-SB-PT</t>
+          <t>Audio Array-B0CKHVHVQ1-AM W45 Wireless-SBV-KT-Phrase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0D3M86SH1</t>
+          <t>B0CKHVHVQ1</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10916</v>
+        <v>19568</v>
       </c>
       <c r="E7" t="n">
-        <v>121</v>
+        <v>85</v>
       </c>
       <c r="F7" t="n">
-        <v>1625.687524309833</v>
+        <v>1245.08</v>
       </c>
       <c r="G7" t="n">
-        <v>5822.171007120328</v>
+        <v>17623.72</v>
       </c>
       <c r="H7" t="n">
         <v>4</v>
@@ -14387,28 +14387,28 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Audio Array-B0BPLZ5CGV-AI 04 Audio Interface-SBV -PT</t>
+          <t>Audio Array-B0CKHVHVQ1-AM W45 Wireless-SBV-KT-Phrase (2)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0CKHVHVQ1</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>82230</v>
+        <v>24086</v>
       </c>
       <c r="E8" t="n">
-        <v>620</v>
+        <v>146</v>
       </c>
       <c r="F8" t="n">
-        <v>5717.33</v>
+        <v>1053.12</v>
       </c>
       <c r="G8" t="n">
-        <v>36602.54</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -14420,7 +14420,7 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Audio Array-B0CKHVHVQ1-AM W45 Wireless-SBV-KT-Phrase</t>
+          <t>Audio Array-B0CKHVHVQ1-AM W45 Wireless-SBV-PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -14429,19 +14429,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>19568</v>
+        <v>60083</v>
       </c>
       <c r="E9" t="n">
-        <v>85</v>
+        <v>465</v>
       </c>
       <c r="F9" t="n">
-        <v>1245.08</v>
+        <v>2410.22</v>
       </c>
       <c r="G9" t="n">
-        <v>17623.72</v>
+        <v>4405.93</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -14453,22 +14453,22 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Audio Array-B0CKHVHVQ1-AM W45 Wireless-SBV-KT-Phrase (2)</t>
+          <t>Audio Array-B0DXFPM4N2-Studio Monitor- SBV-CT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B0CKHVHVQ1</t>
+          <t>B0DXFPM4N2</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>24086</v>
+        <v>19117</v>
       </c>
       <c r="E10" t="n">
-        <v>146</v>
+        <v>249</v>
       </c>
       <c r="F10" t="n">
-        <v>1053.12</v>
+        <v>2475.71</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -14486,28 +14486,28 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Audio Array-B0CKHVHVQ1-AM W45 Wireless-SBV-PT</t>
+          <t>Audio Array-Catch All-Condenser -SB-PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B0CKHVHVQ1</t>
+          <t>B0B4DPX2J2</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>60083</v>
+        <v>13680</v>
       </c>
       <c r="E11" t="n">
-        <v>465</v>
+        <v>143</v>
       </c>
       <c r="F11" t="n">
-        <v>2410.22</v>
+        <v>2123.736666666667</v>
       </c>
       <c r="G11" t="n">
-        <v>4405.93</v>
+        <v>5718.37</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -14519,28 +14519,28 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Audio Array-B0DXFPM4N2-Studio Monitor- SBV-CT</t>
+          <t>Audio Array-Catch All-Condenser -SB-PT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B0DXFPM4N2</t>
+          <t>B0D3M1B4Z8</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>19117</v>
+        <v>13680</v>
       </c>
       <c r="E12" t="n">
-        <v>249</v>
+        <v>143</v>
       </c>
       <c r="F12" t="n">
-        <v>2475.71</v>
+        <v>2123.736666666667</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>5718.37</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -14557,23 +14557,23 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B0B4DPX2J2</t>
+          <t>B0FF9R3GKK</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>21483</v>
+        <v>13680</v>
       </c>
       <c r="E13" t="n">
-        <v>224</v>
+        <v>143</v>
       </c>
       <c r="F13" t="n">
-        <v>3334.949587195885</v>
+        <v>2123.736666666667</v>
       </c>
       <c r="G13" t="n">
-        <v>8979.68</v>
+        <v>5718.37</v>
       </c>
       <c r="H13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -14585,28 +14585,28 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Audio Array-Catch All-Condenser -SB-PT</t>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0D3M1B4Z8</t>
+          <t>B0B4DPX2J2</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13782</v>
+        <v>7369</v>
       </c>
       <c r="E14" t="n">
-        <v>144</v>
+        <v>45</v>
       </c>
       <c r="F14" t="n">
-        <v>2139.576384773983</v>
+        <v>528.3271428571428</v>
       </c>
       <c r="G14" t="n">
-        <v>5761.02</v>
+        <v>2582.203571428571</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -14618,25 +14618,25 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Audio Array-Catch All-Condenser -SB-PT</t>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0FF9R3GKK</t>
+          <t>B0B4DS678Q</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5776</v>
+        <v>7369</v>
       </c>
       <c r="E15" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="F15" t="n">
-        <v>896.684028030132</v>
+        <v>528.3271428571428</v>
       </c>
       <c r="G15" t="n">
-        <v>2414.41</v>
+        <v>2582.203571428571</v>
       </c>
       <c r="H15" t="n">
         <v>1</v>
@@ -14656,23 +14656,23 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0B4DPX2J2</t>
+          <t>B0B4G19R58</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>26124</v>
+        <v>7369</v>
       </c>
       <c r="E16" t="n">
-        <v>136</v>
+        <v>45</v>
       </c>
       <c r="F16" t="n">
-        <v>2020.133718092619</v>
+        <v>528.3271428571428</v>
       </c>
       <c r="G16" t="n">
-        <v>6734.760000000001</v>
+        <v>2582.203571428571</v>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -14689,23 +14689,23 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0B4K87PR4</t>
+          <t>B0B4G1PXWV</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>28565</v>
+        <v>7369</v>
       </c>
       <c r="E17" t="n">
-        <v>144</v>
+        <v>45</v>
       </c>
       <c r="F17" t="n">
-        <v>1227.582149132192</v>
+        <v>528.3271428571428</v>
       </c>
       <c r="G17" t="n">
-        <v>6777.959999999999</v>
+        <v>2582.203571428571</v>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -14722,23 +14722,23 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0BLJVJ2GN</t>
+          <t>B0B4JRQP22</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1153</v>
+        <v>7369</v>
       </c>
       <c r="E18" t="n">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="F18" t="n">
-        <v>242.4426520898196</v>
+        <v>528.3271428571428</v>
       </c>
       <c r="G18" t="n">
-        <v>550</v>
+        <v>2582.203571428571</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -14755,23 +14755,23 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0B4K87PR4</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>49179</v>
+        <v>7369</v>
       </c>
       <c r="E19" t="n">
-        <v>372</v>
+        <v>45</v>
       </c>
       <c r="F19" t="n">
-        <v>4289.9</v>
+        <v>528.3271428571428</v>
       </c>
       <c r="G19" t="n">
-        <v>30713.57</v>
+        <v>2582.203571428571</v>
       </c>
       <c r="H19" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -14788,23 +14788,23 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0CF5TCQKL</t>
+          <t>B0B4KC7VBM</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13566</v>
+        <v>7369</v>
       </c>
       <c r="E20" t="n">
-        <v>149</v>
+        <v>45</v>
       </c>
       <c r="F20" t="n">
-        <v>2852.52734791018</v>
+        <v>528.3271428571428</v>
       </c>
       <c r="G20" t="n">
-        <v>6471.18</v>
+        <v>2582.203571428571</v>
       </c>
       <c r="H20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -14821,23 +14821,23 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0CKHVHVQ1</t>
+          <t>B0BLJVJ2GN</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>74272</v>
+        <v>7369</v>
       </c>
       <c r="E21" t="n">
-        <v>376</v>
+        <v>45</v>
       </c>
       <c r="F21" t="n">
-        <v>3191.899048283553</v>
+        <v>528.3271428571428</v>
       </c>
       <c r="G21" t="n">
-        <v>17623.72</v>
+        <v>2582.203571428571</v>
       </c>
       <c r="H21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -14854,20 +14854,20 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0D3LZWTHV</t>
+          <t>B0BLK8DNPD</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11338</v>
+        <v>7369</v>
       </c>
       <c r="E22" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="F22" t="n">
-        <v>876.7362819073812</v>
+        <v>528.3271428571428</v>
       </c>
       <c r="G22" t="n">
-        <v>2922.88</v>
+        <v>2582.203571428571</v>
       </c>
       <c r="H22" t="n">
         <v>1</v>
@@ -14887,25 +14887,619 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>B0BPLZ5CGV</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>7369</v>
+      </c>
+      <c r="E23" t="n">
+        <v>45</v>
+      </c>
+      <c r="F23" t="n">
+        <v>528.3271428571428</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2582.203571428571</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>B0C4YTNJG7</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>7369</v>
+      </c>
+      <c r="E24" t="n">
+        <v>45</v>
+      </c>
+      <c r="F24" t="n">
+        <v>528.3271428571428</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2582.203571428571</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>B0C539RBGL</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>7369</v>
+      </c>
+      <c r="E25" t="n">
+        <v>45</v>
+      </c>
+      <c r="F25" t="n">
+        <v>528.3271428571428</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2582.203571428571</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>B0CF5R3V95</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>7369</v>
+      </c>
+      <c r="E26" t="n">
+        <v>45</v>
+      </c>
+      <c r="F26" t="n">
+        <v>528.3271428571428</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2582.203571428571</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>B0CF5RRTDJ</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>7369</v>
+      </c>
+      <c r="E27" t="n">
+        <v>45</v>
+      </c>
+      <c r="F27" t="n">
+        <v>528.3271428571428</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2582.203571428571</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>B0CF5TCQKL</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>7369</v>
+      </c>
+      <c r="E28" t="n">
+        <v>45</v>
+      </c>
+      <c r="F28" t="n">
+        <v>528.3271428571428</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2582.203571428571</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>B0CH4RT4P8</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>7369</v>
+      </c>
+      <c r="E29" t="n">
+        <v>45</v>
+      </c>
+      <c r="F29" t="n">
+        <v>528.3271428571428</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2582.203571428571</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>B0CKHVHVQ1</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>7369</v>
+      </c>
+      <c r="E30" t="n">
+        <v>45</v>
+      </c>
+      <c r="F30" t="n">
+        <v>528.3271428571428</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2582.203571428571</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>B0CM6NTWBP</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>7369</v>
+      </c>
+      <c r="E31" t="n">
+        <v>45</v>
+      </c>
+      <c r="F31" t="n">
+        <v>528.3271428571428</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2582.203571428571</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>B0D3M1B4Z8</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>7369</v>
+      </c>
+      <c r="E32" t="n">
+        <v>45</v>
+      </c>
+      <c r="F32" t="n">
+        <v>528.3271428571428</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2582.203571428571</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>B0DFMLS8JG</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>7369</v>
+      </c>
+      <c r="E33" t="n">
+        <v>45</v>
+      </c>
+      <c r="F33" t="n">
+        <v>528.3271428571428</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2582.203571428571</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>B0DFMMTWLY</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>7369</v>
+      </c>
+      <c r="E34" t="n">
+        <v>45</v>
+      </c>
+      <c r="F34" t="n">
+        <v>528.3271428571428</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2582.203571428571</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>B0DFMNGFTD</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>7369</v>
+      </c>
+      <c r="E35" t="n">
+        <v>45</v>
+      </c>
+      <c r="F35" t="n">
+        <v>528.3271428571428</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2582.203571428571</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
           <t>B0DT6T6N6B</t>
         </is>
       </c>
-      <c r="D23" t="n">
-        <v>2139</v>
-      </c>
-      <c r="E23" t="n">
-        <v>11</v>
-      </c>
-      <c r="F23" t="n">
-        <v>91.93880258425463</v>
-      </c>
-      <c r="G23" t="n">
-        <v>507.63</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="inlineStr">
+      <c r="D36" t="n">
+        <v>7369</v>
+      </c>
+      <c r="E36" t="n">
+        <v>45</v>
+      </c>
+      <c r="F36" t="n">
+        <v>528.3271428571428</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2582.203571428571</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>B0FF9R3GKK</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>7369</v>
+      </c>
+      <c r="E37" t="n">
+        <v>45</v>
+      </c>
+      <c r="F37" t="n">
+        <v>528.3271428571428</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2582.203571428571</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>B0G2C2RCXN</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>7369</v>
+      </c>
+      <c r="E38" t="n">
+        <v>45</v>
+      </c>
+      <c r="F38" t="n">
+        <v>528.3271428571428</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2582.203571428571</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>B0G3Q517Y2</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>7369</v>
+      </c>
+      <c r="E39" t="n">
+        <v>45</v>
+      </c>
+      <c r="F39" t="n">
+        <v>528.3271428571428</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2582.203571428571</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>B0G3Q59X8C</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>7369</v>
+      </c>
+      <c r="E40" t="n">
+        <v>45</v>
+      </c>
+      <c r="F40" t="n">
+        <v>528.3271428571428</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2582.203571428571</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>B0G4DNF8RZ</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>7369</v>
+      </c>
+      <c r="E41" t="n">
+        <v>45</v>
+      </c>
+      <c r="F41" t="n">
+        <v>528.3271428571428</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2582.203571428571</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" t="inlineStr">
         <is>
           <t>Audio Array</t>
         </is>
